--- a/django_app/constructing_report.xlsx
+++ b/django_app/constructing_report.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,4002 +459,3891 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ресторан на пр.Науки (Митхед)</t>
+          <t>Производственный холдинг</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2-24707</t>
+          <t>5-24571</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>пн920</t>
+          <t>чп347_1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Кресло баран /FP/ Изделие №920 (02, 890*750*h940 мм)</t>
+          <t>Диван радиусный без скоса /ЧП/ Изделие №347 (06, 1100)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>130998.29</v>
+        <v>38250</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>45779</v>
+        <v>45868</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ресторан на пр.Науки (Митхед)</t>
+          <t>Производственный холдинг</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11-24707</t>
+          <t>6-24571</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>пн920</t>
+          <t>чп347_1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Подушка (тубус) /FP/ Изделие №920 (11)</t>
+          <t>Диван радиусный без скоса /ЧП/ Изделие №347 (07, 1100)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>38250</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>45776</v>
+        <v>45876</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>УК ПЛАЗА YES</t>
+          <t>Производственный холдинг</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1-24798</t>
+          <t>7-24571</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>пн918</t>
+          <t>чп347_1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Диван реплика Minotti Brasilia /FP/ Изделие №918 (01, 3500*980*h850 мм)</t>
+          <t>Диван радиусный со скосом /ЧП/ Изделие №347 (08, 1190)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>195000</v>
+        <v>42300</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45789</v>
+        <v>45868</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Владислав Букин</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>УК ПЛАЗА YES</t>
+          <t>Производственный холдинг</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2-24798</t>
+          <t>8-24571</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>пн918</t>
+          <t>чп347_1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Кресло реплика Minotti Brasilia /FP/ Изделие №918 (02, 950*860*h850 мм)</t>
+          <t>Диван радиусный со скосом /ЧП/ Изделие №347 (09, 1190)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>110000</v>
+        <v>42300</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>45784</v>
+        <v>45876</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Владислав Букин</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>УК ПЛАЗА YES</t>
+          <t>Сокольники</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3-24798</t>
+          <t>2-24872</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>пн918</t>
+          <t>пн0050</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Столик реплика Minotti Superquadra /FP/ Изделие №918 (03, 1600*575*h220 мм)</t>
+          <t>Кровать реплика "ALYS 207-212-H92" / FP / Изделие №572_5322 / (16)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>150000</v>
+        <v>280000</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>45782</v>
+        <v>45841</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Владислав Букин</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>УК ПЛАЗА YES</t>
+          <t>Сокольники</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4-24798</t>
+          <t>4-24872</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>пн918</t>
+          <t>пн0050</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Пуф реплика Minotti Brasilia /FP/ Изделие №918 (04, 980*600*h420 мм)</t>
+          <t>Кровать реплика Calligaris MIES MIX /СЗМК/ Изделие №0050 (01, под матрас 1400*2000 мм)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>78000</v>
+        <v>150000</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>45783</v>
+        <v>45868</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Владислав Букин</t>
+          <t>Букин Владислав</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>УК ПЛАЗА YES</t>
+          <t>Сокольники</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5-24798</t>
+          <t>6-24872</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>пн918</t>
+          <t>пн0050</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Стул реплика Molteni &amp; C Barbican /FP/ Изделие №918 (05, 630*620*h830 мм)</t>
+          <t>Кровать /СЗМК/ Изделие №0050 (03, под матрас 1400х2000 мм)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>49000</v>
+        <v>128000</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>45796</v>
+        <v>45852</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Сапачук Елизавета</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>УК ПЛАЗА YES</t>
+          <t>Евгения от Петракова</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6-24798</t>
+          <t>1-24936</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>пн918</t>
+          <t>пн459</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Полка с подсветкой и бокс для грязных полотенец /FP/ Изделие №918 (06, дл 860 мм)</t>
+          <t>Пуф /ЧП/ Изделия №0459 (01)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30000</v>
+        <v>48550</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>45825</v>
+        <v>45839</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Сапачук Елизавета</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>УК ПЛАЗА YES</t>
+          <t>Евгения от Петракова</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7-24798</t>
+          <t>2-24936</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>пн918</t>
+          <t>пн459</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Полка с подсветкой и бокс для грязных полотенец /FP/ Изделие №918 (07, дл 780 мм)</t>
+          <t>Кресло /ЧП/ Изделия №0459 (02)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>30000</v>
+        <v>74650</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>45825</v>
+        <v>45868</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Сапачук Елизавета</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMO (КОМО)</t>
+          <t>Летниковка</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1-24861</t>
+          <t>20-23925</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0102</t>
+          <t>пн663</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Кровать Siena Kids (COMO)  с широким L образным изголовьем (1820*3330*620) 1200*2000мм</t>
+          <t>Стол реплика Studio Twentyseven (Стол Eros) /FP/ Изделие №663 (16,1800*450*h720 мм)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>83500</v>
+        <v>380000</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>45762</v>
+        <v>45919</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Сокольники</t>
+          <t>UNO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5-24872</t>
+          <t>9-23815</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>пн0050</t>
+          <t>пн599_5959</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Стул Adelaide Chair /СЗМК/ Изделие №0050 (02, без колес)</t>
+          <t>Кровать /FP/ Изделие №599 (Вариант №6)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>48000</v>
+        <v>40800</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>45825</v>
+        <v>45887</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ярошевич</t>
+          <t>UNO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1-24878</t>
+          <t>23-23815</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>пн946</t>
+          <t>пн599_5959</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Диван /FP/ Изделие №946 (01, ш1800*950 мм)</t>
+          <t>Кровать /FP/ Изделие №599 (Вариант №10)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>310600</v>
+        <v>40100</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>45776</v>
+        <v>45887</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Тихая Гавань (Геленджик)</t>
+          <t>UNO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1-24891</t>
+          <t>24-23815</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>пн443_1</t>
+          <t>пн599_5959</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Пуфик со спинкой (без вращения) /1мф/ Изделие №443 (08, 720*480*480 мм)</t>
+          <t>Кровать /FP/ Изделие №599 (Вариант №11)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>23700</v>
+        <v>40100</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>45748</v>
+        <v>45883</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Елизавета Сапачук</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Аппарт Отель Омега (1мф)</t>
+          <t>UNO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1-24914</t>
+          <t>25-23815</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>пн459</t>
+          <t>пн599_5959</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Мягкие элементы изголовья /1мф/ Изделие №0459 (01, 653*380*30 мм)</t>
+          <t>Кровать /FP/ Изделие №599 (Вариант №12)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4200</v>
+        <v>41700</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>45751</v>
+        <v>45887</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Аппарт Отель Омега (1мф)</t>
+          <t>UNO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2-24914</t>
+          <t>26-23815</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>пн459</t>
+          <t>пн599_5959</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Мягкие элементы изголовья /1мф/ Изделие №0459 (02, 440*380*30 мм)</t>
+          <t>Кровать /FP/ Изделие №599 (Вариант №13)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5200</v>
+        <v>40100</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>45751</v>
+        <v>45883</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Грибоедова (ДОРОС)</t>
+          <t>UNO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1-24916</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>пн0062Пилот</t>
-        </is>
-      </c>
+          <t>1-24023</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Спринг бокс 900*2000*h350 мм (высота борта 270 мм, ножка 80 мм)</t>
+          <t>Кушетка /FP/ Изделие №599_5959 (04, 1940*840*300 мм)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14300</v>
+        <v>25900</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>45748</v>
+        <v>45919</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Грибоедова (ДОРОС)</t>
+          <t>Mercure Алтай</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7-24916</t>
+          <t>1-24999</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>пн0062Пилот</t>
+          <t>пн777_2Пилот</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Кресло раскладное Грибоедова (01, 900*900(1800)*h560 мм)</t>
+          <t>Изголовье (Мягкий элемент) /FP/ Изделие №777 (05, 3400*2300 мм)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>35000</v>
+        <v>43900</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>45760</v>
+        <v>45855</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Букин Владислав</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FLUFFY&amp;PUFFY</t>
+          <t>Mercure Алтай</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1-24924</t>
+          <t>2-24999</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>пн945</t>
+          <t>пн777_2Пилот</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Стеновая панель 1520*1520 мм /FP/ Изделие №945 (01)</t>
+          <t>Основание /FP/ Изделие №777 (06, 2000*2000 мм)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5200</v>
+        <v>33300</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>45754</v>
+        <v>45866</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Сапачук Елизавета</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Рыжий</t>
+          <t>Mercure Алтай</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1-24925</t>
+          <t>3-24999</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>пн104р</t>
+          <t>пн777_2Пилот</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Услуги по перетяжке и обивке (49, бокс 1600*2000*350 мм, ВАЛА)</t>
+          <t>Диван с одним локтем /FP/ Изделие №777 (07, 1950*900*h920 мм)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3500</v>
+        <v>59500</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>45757</v>
+        <v>45868</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Сокольники</t>
+          <t>Туник Ульяна</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1-24927</t>
+          <t>1-25029</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>пн0050_1</t>
+          <t>пн0408</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Услуги по перетяжке и обивке (50, диван)</t>
+          <t>Стул обеденный Fn-1 /ЧП/ Изделие №0408 (01)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>42968.75</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>45777</v>
+        <v>45859</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Разовый заказ</t>
+          <t>Туник Ульяна</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1-24929</t>
+          <t>2-25029</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>пн105р</t>
+          <t>пн0408</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Подушка 1250*70*h130 мм</t>
+          <t>Стул Fn-16 /ЧП/ Изделие №0408 (02)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1000</v>
+        <v>42875</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>45778</v>
+        <v>45868</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Грибоедова (ДОРОС)</t>
+          <t>Авенир Ладожский 1МФ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3-24916</t>
+          <t>4-25034</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>пн0062Пилот</t>
+          <t>пн353_5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Мягкие элементы изголовья Грибоедов (ДОРОС) (01, 2010x405x20 мм)</t>
+          <t>Изголовье /1мф/ Изделие №353  (03, 2110*50*h1030 мм с БРУСКАМИ)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>29000</v>
+        <v>22900</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>45757</v>
+        <v>45868</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>COMO (КОМО)</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1-24923</t>
+          <t>1-25041</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>00109</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Кровать Siena ( увеличенное двойное тонкое изголовье) 1800*2000 (2020*2620)</t>
+          <t>Евро-диван / "Манчестер" / База / (сп.м. 1500*2000, накладки шимо)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>120000</v>
+        <v>44200</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>45757</v>
+        <v>45841</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>УК Летниковка</t>
+          <t>Марриотт</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1-24933</t>
+          <t>1-25032</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>пн0923</t>
+          <t>пн595_2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Кресло Silver Brice</t>
+          <t>Изголовье / FP / Изделие №595 (01, 1900*1500 мм)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>58000</v>
+        <v>46850</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>45771</v>
+        <v>45852</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Сапачук Елизавета</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>УК Летниковка</t>
+          <t>Грибоедова (1МФ)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2-24933</t>
+          <t>3-25039</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>пн0923</t>
+          <t>пн0465_1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Столик /FP/ Изделие №0923 (01)</t>
+          <t>Пуф Грибоедов /1мф/ Изделие № 0451 (01, 800-900*h450 мм)</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>25000</v>
+        <v>12800</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>45791</v>
+        <v>45839</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Елизавета Сапачук</t>
+          <t>Сапачук Елизавета</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Лобби Летниковка</t>
+          <t>Грибоедова (ДОРОС)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2-24932</t>
+          <t>4-25060</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>пн0073</t>
+          <t>пн0062Пилот2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Диван реплика Molteni&amp;C Surf (2800*1120*710 мм)</t>
+          <t>Банкетка Грибоедов Дорос (03, 800*500*h450 мм)</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>233000</v>
+        <v>12100</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>45831</v>
+        <v>45839</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Владислав Букин</t>
+          <t>Сапачук Елизавета</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Лобби Летниковка</t>
+          <t>Подиумы</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3-24932</t>
+          <t>1-25058</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>пн0073</t>
+          <t>пн959</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Диван реплика Molteni&amp;C Surf (3900*1120*710 мм)</t>
+          <t>Подиум Швеция, ДУБ /FP/ (1590*670*210 мм)</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>298000</v>
+        <v>17100</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>45831</v>
+        <v>45840</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Владислав Букин</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Лобби Летниковка</t>
+          <t>Рыжий</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4-24932</t>
+          <t>2-24925</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>пн0073</t>
+          <t>пн104р</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Диван Korduda Sofa Model (3450 мм)</t>
+          <t>Услуги по перетяжке и обивке (57, бокс 1000*2000*350 мм, ВАЛА)</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>295000</v>
+        <v>2550</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>45775</v>
+        <v>45847</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Елизавета Сапачук</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Лобби Летниковка</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5-24932</t>
+          <t>1-25075</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>пн0073</t>
+          <t>С-1760</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Кресло UNO2</t>
+          <t>Угловой диван / "Монреаль" / База / (сп.м. 1,9х1,5 м, ф. Г, мягкий)</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>55000</v>
+        <v>48400</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>45769</v>
+        <v>45841</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Авенир Ладожский 1МФ</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1-24935</t>
+          <t>1-25076</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>пн353_2</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Изголовье /1мф/ Изделие №353  (02, 2110*50*h1030 мм)</t>
+          <t>Кровать Siena стандартное (одинарное) тонкое изголовье с подъемным механизмом 2330*1620х670h (1400*2000 мм)</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>22900</v>
+        <v>92500</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>45756</v>
+        <v>45855</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Авенир Ладожский 1МФ</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3-24935</t>
+          <t>1-25077</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>пн353_2</t>
+          <t>С-1761</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Подушка (подбагажница) (800*450*50 мм)</t>
+          <t>Минитахта / "Прага" / База / (ш. 1,8 м)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4900</v>
+        <v>30100</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>45756</v>
+        <v>45853</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>УК Летниковка</t>
+          <t>Наталья Мебель Маркет СПБ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3-24933</t>
+          <t>1-25045</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>пн0923</t>
+          <t>пн0002</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Услуги по ремонту (16, столика)</t>
+          <t>Евро-диван / "Монреаль" / База / (сп.м. 1,9х1,5 м, ш.подл. 70 мм)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>115200</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>45777</v>
+        <v>45847</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ПАРФЕНЬЕВ ЕГОР (Максим 1мф)</t>
+          <t>Наталья Мебель Маркет СПБ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1-24931</t>
+          <t>2-25045</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>пн0001</t>
+          <t>пн0002</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Экран разделительный /СУЛ/ Изделие №0001 (01, 1580*450*16 мм)</t>
+          <t>Кресло /СУЛ/ Изделие №0001 (02, 750*750*h805 мм)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>7600</v>
+        <v>39200</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>45777</v>
+        <v>45847</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Елизавета Сапачук</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ПАРФЕНЬЕВ ЕГОР (Максим 1мф)</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2-24931</t>
+          <t>1-25083</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>пн0001</t>
+          <t>Рекламация</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Экран разделительный /СУЛ/ Изделие №0001 (02, 1380*450*16 мм)</t>
+          <t>Услуги по перетяжке и обивке диван "Люксембург"</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6700</v>
+        <v>0</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>45777</v>
+        <v>45847</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Елизавета Сапачук</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ПАРФЕНЬЕВ ЕГОР (Максим 1мф)</t>
+          <t>Подиумы</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3-24931</t>
+          <t>1-25085</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>пн0001</t>
+          <t>пн960</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Экран разделительный /СУЛ/ Изделие №0001 (03, 1670*450*16 мм)</t>
+          <t>Подиум Белпорт, дуб /FP/ Изделие № 960 (01, 1580*480*150 мм)</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>45777</v>
+        <v>45855</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Елизавета Сапачук</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ПАРФЕНЬЕВ ЕГОР (Максим 1мф)</t>
+          <t>Наталья Мебель Маркет СПБ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4-24931</t>
+          <t>1-25093</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>пн0001</t>
+          <t>пн0012</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Экран разделительный /СУЛ/ Изделие №0001 (04, 690*450*16 мм)</t>
+          <t>Диван не раскладной /СУЛ/ Изделие №0012 (01, 2700* 900*H 840 мм)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3500</v>
+        <v>104345.78</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>45777</v>
+        <v>45868</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Елизавета Сапачук</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ярошевич</t>
+          <t>Наталья Мебель Маркет СПБ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1-24937</t>
+          <t>2-25093</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>пн946</t>
+          <t>пн0012</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Кресло /FP/ Изделие № 0943 (01)</t>
+          <t>Кровать /ЧП/ Изделие №121 (09, 1800*2100 мм)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>85000</v>
+        <v>55126.07</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>45820</v>
+        <v>45868</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Серийная мебель</t>
+          <t>Наталья Мебель Маркет СПБ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1-24941</t>
+          <t>3-25093</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>с-1659</t>
+          <t>пн0012</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Евро-диван / "Монреаль" / База / (сп.м. 1,5x2,0 мм, ш.подл. 120 мм, мягкие)</t>
+          <t>Кресло /ЧП/ Изделие №121 (02, 1100*900 мм)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>40600</v>
+        <v>68907.59</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>45771</v>
+        <v>45868</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Рессо</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2-24956</t>
+          <t>6-25078</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>пн433</t>
+          <t>062</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Изголовье /ЧП/ Изделие №433 (01, ш2900*в900*толщ 60 мм)</t>
+          <t>Кровать Siena fly  с креплением к стене без панелей 2220*2530*670 (1800*2000)</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>20000</v>
+        <v>98000</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>45765</v>
+        <v>45884</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Рессо</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3-24956</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>пн433</t>
-        </is>
-      </c>
+          <t>1-25105</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Кровать модель Кейдж /ЧП/ Изделие №0433 (02, 2100*2440*h900 мм)</t>
+          <t>Изголовье для кровати 2190*30*900</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>80000</v>
+        <v>15000</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>45764</v>
+        <v>45895</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Рессо</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4-24956</t>
+          <t>1-25095</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>пн433</t>
+          <t>0130</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Кровать модель Кейдж /ЧП/ Изделие №0433 (03, 2200*2440*h900 мм)</t>
+          <t>Основание детской кровати Siena Kids с Тонким  П образным изголовьем (1110*2330*h670мм, 900*2000 мм)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>83200</v>
+        <v>88000</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>45764</v>
+        <v>45860</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Рессо</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5-24956</t>
+          <t>1-25099</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>пн433</t>
+          <t>00120</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Мастер кровать /ЧП/ Изделие №0433 (04, спал.место 2000*1800 мм)</t>
+          <t>Кровать Siena(основание из 2 частей), увеличенное тонкое одинарное изг. (2820*2330*670_) 2000*2000</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>93000</v>
+        <v>123000</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>45767</v>
+        <v>45877</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Рессо</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6-24956</t>
+          <t>1-25106</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>пн433</t>
+          <t>0124</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Стеновая панель прямолинейная /ЧП/ Изделие №0433 (05, В2943хШ2000)</t>
+          <t>Модуль FLAT Classic 1600*1000*400 опоры Массив</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>150000</v>
+        <v>53000</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>45767</v>
+        <v>45894</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Рессо</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7-24956</t>
+          <t>1-25102</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>пн433</t>
+          <t>00122</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Банкетка /ЧП/ Изделие №0433 (06)</t>
+          <t>Кровать Siena Fly (COMO) стандартное одинарное тонкое изголовье 2020х2330х670h  ( 1800*2000)</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>29000</v>
+        <v>98000</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>45768</v>
+        <v>45882</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Грибоедова (ДОРОС)</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1-24957</t>
+          <t>4-25102</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>пн0062_1Пилот</t>
+          <t>00122</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Мягкий элемент изголовья Грибоедов (ДОРОС) (03, 1400x400 мм с закругленным верхом)</t>
+          <t>Модуль FLAT 2000*1000*400 опоры Slot</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>45771</v>
+        <v>45876</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Подиумы</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1-24874</t>
+          <t>10-25102</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>пн953</t>
+          <t>00122</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Подиум Швеция, ДУБ /FP/ (1575*1150*140 мм)</t>
+          <t>Кровать Siena kids(como) с тонким Г образным изголовьем, с подъемным механизмом (1200*2000), 1620*330*670)</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>16700</v>
+        <v>83000</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>45775</v>
+        <v>45898</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Подиумы</t>
+          <t>Гостиница Чечня</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2-24874</t>
+          <t>1-25110</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>пн953</t>
+          <t>пн 0085</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Подиум Швеция, ДУБ /FP/ (1035*795*140 мм)</t>
+          <t>Спринг бокс /СЗМК/ Изделие №0085 (01, 800*2000*h350 мм) высота борта - 250 мм, ножка - 100 мм</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>13700</v>
+        <v>16400</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>45775</v>
+        <v>45860</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ресторан на пр.Науки (Митхед)</t>
+          <t>Гостиница Чечня</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>9-24707</t>
+          <t>2-25110</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>пн920</t>
+          <t>пн 0085</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Диван sof-03 /FP/ Изделие №920 (09, 2140*880*780 мм)</t>
+          <t>Изголовье (мягкий элемент) /СЗМК/ Изделие №0085 (02, 1200*1900*толщ50 мм)</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>186248.27</v>
+        <v>16100</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>45775</v>
+        <v>45860</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Админ СЗМК</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Подиумы</t>
+          <t>Разовый заказ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1-24962</t>
+          <t>1-25112</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>пн954</t>
+          <t>пн0484</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Подиум Швеция, ДУБ /FP/ (1745*1115*140 мм)</t>
+          <t>Мягкий элемент /1мф/ Изделие №0484 (01, 1203х400х60 мм)</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>17800</v>
+        <v>22400</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>45777</v>
+        <v>45888</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Подиумы</t>
+          <t>Завидово</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2-24962</t>
+          <t>1-25114</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>пн954</t>
+          <t>пн0475</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Подиум Швеция, ДУБ /FP/ (1635*860*140 мм)</t>
+          <t>Подбагажница /1мф/ Изделие № 0475 (01, 800*536*40 мм)</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>16300</v>
+        <v>6300</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>45777</v>
+        <v>45870</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Подиумы</t>
+          <t>Статио Проджект</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1-24963</t>
+          <t>1-25094</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>пн955</t>
+          <t>пн0366</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Подиум Швеция, ДУБ /FP/ (1805*1115*140 мм)</t>
+          <t>Пуф /СМ/ Изделие №0366 (01, d450*h500 мм)</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>18000</v>
+        <v>6650</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>45776</v>
+        <v>45868</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Подиумы</t>
+          <t>Магазин СЗМК pro</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2-24963</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>пн955</t>
-        </is>
-      </c>
+          <t>2-25021</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Подиум Швеция, ДУБ /FP/ (1685*890*140 мм)</t>
+          <t>Евро диван / "Пионер" / База / (сп.м. 1,9х1,5 м, подл. низкие)</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>16700</v>
+        <v>0</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>45777</v>
+        <v>45869</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>СЗМК Админ</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Подиумы</t>
+          <t>Kempinsky Erevan</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1-24969</t>
+          <t>1-33133</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>пн957</t>
+          <t>пн0012</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Подиум Швеция, ДУБ /FP/ (2105*1095*140 мм)</t>
+          <t>Стул Kempinski /NOV/ Изделие №0012 (01)</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>18800</v>
+        <v>0</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>45777</v>
+        <v>45883</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Подиумы</t>
+          <t>Грибоедова (ДОРОС)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2-24969</t>
+          <t>1-33135</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>пн957</t>
+          <t>пн0115</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Подиум Швеция, ДУБ /FP/ (1600*1040*140 мм)</t>
+          <t>Ножка дубовая Грибоедово /СЗМК/ Изделие №0115 (01, 650*90*30 мм)</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>17000</v>
+        <v>2500</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>45777</v>
+        <v>45876</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>UNO</t>
+          <t>Архыз</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12-23815</t>
+          <t>1-33139</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>пн599_5959</t>
+          <t>пн0477</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Кровать /FP/ Изделие №599 (Вариант №5)</t>
+          <t>Основание /1мф/ Изделие № 0477 (01, 2000*1000 мм)</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>34800</v>
+        <v>16500</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>45778</v>
+        <v>45876</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>UNO</t>
+          <t>Архыз</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>13-23815</t>
+          <t>2-33139</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>пн599_5959</t>
+          <t>пн0477</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Кровать /FP/ Изделие №599 (Вариант №7)</t>
+          <t>Изголовье /1мф/ Изделие № 0477 (02, 1000*1000 мм)</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>34800</v>
+        <v>9400</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>45778</v>
+        <v>45882</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>UNO</t>
+          <t>Архыз</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>14-23815</t>
+          <t>3-33139</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>пн599_5959</t>
+          <t>пн0477</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Кровать /FP/ Изделие №599 (Вариант №8)</t>
+          <t>Пуф /1мф/ Изделие № 0477 (03, 450*400*350 мм)</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>34800</v>
+        <v>23000</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>45778</v>
+        <v>45883</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>UNO</t>
+          <t>Разовый заказ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15-23815</t>
+          <t>1-33142</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>пн599_5959</t>
+          <t>пн0483</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Кровать /FP/ Изделие №599 (Вариант №9)</t>
+          <t>Мягкий элемент /1мф/ Изделие № 0483 (01,1600 х 450 х h450 мм)</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>34800</v>
+        <v>25000</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>45778</v>
+        <v>45888</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Букин Владислав</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>UNO</t>
+          <t>Маркет плейсы</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16-23815</t>
+          <t>1-33143</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>пн599_5959</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Кровать /FP/ Изделие №599 (Вариант №14)</t>
+          <t>Спринг бокс 1200*1900</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>34800</v>
+        <v>20400</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>45778</v>
+        <v>45877</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Букин Владислав</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Разовый заказ</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1-24792</t>
+          <t>2-33144</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>пн386</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Панель /ЧП/ Изделие № 386 (01, h1380 мм)</t>
+          <t>Подушка к дивану Люксембург</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>138000</v>
+        <v>0</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>45804</v>
+        <v>45888</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Разовый заказ</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2-24792</t>
+          <t>1-33149</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>пн386</t>
+          <t>В зал</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Кроватное основание /ЧП/ Изделие № 386 (02)</t>
+          <t>Евро-диван / "Манчестер" / База / (сп.м. 2,0х1,5 м, стол)</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>155000</v>
+        <v>47900</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>45827</v>
+        <v>45882</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ПАРФЕНЬЕВ ЕГОР (Максим 1мф)</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1-24958</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>пн0001_1</t>
-        </is>
-      </c>
+          <t>1-33150</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Мягкие элементы /СУЛ/ Изделие №001 (05, 1670*784*428 мм)</t>
+          <t>Перетяжка углового дивана Монреаль</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53500</v>
+        <v>0</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>45824</v>
+        <v>45882</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ПАРФЕНЬЕВ ЕГОР (Максим 1мф)</t>
+          <t>Грибоедова (ДОРОС)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2-24958</t>
+          <t>1-33152</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>пн0001_1</t>
+          <t>пн0115_1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Мягкие элементы /СУЛ/ Изделие №001 (06, 590*4880*484 мм)</t>
+          <t>Услуги по перекраске ножки дубовой Грибоедово /СЗМК/ Изделие №0115 (01, 650*90*30 мм)</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>109300</v>
+        <v>1300</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>45818</v>
+        <v>45883</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ПАРФЕНЬЕВ ЕГОР (Максим 1мф)</t>
+          <t>Завидово</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3-24958</t>
+          <t>1-33146</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>пн0001_1</t>
+          <t>пн0475_1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Мягкие элементы /СУЛ/ Изделие №001 (07, 1715*1150*1270 мм)</t>
+          <t>Спринг бокс (900*2000 мм) с усиленной фиксацией</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>72500</v>
+        <v>13300</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>45825</v>
+        <v>45882</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ПАРФЕНЬЕВ ЕГОР (Максим 1мф)</t>
+          <t>Завидово</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4-24958</t>
+          <t>2-33146</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>пн0001_1</t>
+          <t>пн0475_1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Мягкие элементы /СУЛ/ Изделие №001 (08, 460*3569*4699 мм)</t>
+          <t>Изголовье /1мф/ Изделие № 0475 (02, ш900*в883 мм) с креплением к боксу</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>147300</v>
+        <v>9100</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>45818</v>
+        <v>45882</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ПАРФЕНЬЕВ ЕГОР (Максим 1мф)</t>
+          <t>Завидово</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5-24958</t>
+          <t>4-33146</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>пн0001_1</t>
+          <t>пн0475_1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Мягкие элементы /СУЛ/ Изделие №001 (09, 1299*2672*450 мм)</t>
+          <t>Изголовье /1мф/ Изделие № 0475 (03, ш1800*в883 мм)</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>118800</v>
+        <v>16900</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>45821</v>
+        <v>45882</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ПАРФЕНЬЕВ ЕГОР (Максим 1мф)</t>
+          <t>Завидово</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>6-24958</t>
+          <t>6-33146</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>пн0001_1</t>
+          <t>пн0475_1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Мягкие элементы /СУЛ/ Изделие №001 (10, 1299*768*408 мм)</t>
+          <t>Изголовье /1мф/ Изделие № 0475 (04, ш1600*в1035 мм)</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>49300</v>
+        <v>15700</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>45821</v>
+        <v>45882</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ПАРФЕНЬЕВ ЕГОР (Максим 1мф)</t>
+          <t>РОСКОСМОС</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7-24958</t>
+          <t>1-33156</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>пн0001_1</t>
+          <t>пн0453_4</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Мягкие элементы /СУЛ/ Изделие №001 (11, 570*1400*484 мм)</t>
+          <t>Пуф прямоугольный /ЧП/ Изделие № 0453 (04, 800*400*450 мм)</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>37100</v>
+        <v>8750</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>45818</v>
+        <v>45889</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Букин Владислав</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ПАРФЕНЬЕВ ЕГОР (Максим 1мф)</t>
+          <t>РОСКОСМОС</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>8-24958</t>
+          <t>3-33156</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>пн0001_1</t>
+          <t>пн0453_4</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Мягкие элементы /СУЛ/ Изделие №001 (12, 480*1000*484 мм)</t>
+          <t>Кресло Винг с высокой спинкой /ЧП/ Изделие № 0453 (05, 665*750*1280 мм)</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>37100</v>
+        <v>55000</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>45818</v>
+        <v>45903</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ПАРФЕНЬЕВ ЕГОР (Максим 1мф)</t>
+          <t>РОСКОСМОС</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>9-24958</t>
+          <t>4-33156</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>пн0001_1</t>
+          <t>пн0453_4</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Мягкие элементы /СУЛ/ Изделие №001 (13, 570*1000*484 мм)</t>
+          <t>Диван с высокой спинкой /ЧП/ Изделие № 0453 (06, 1440*800*1370 мм)</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>25000</v>
+        <v>55000</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>45818</v>
+        <v>45895</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ПАРФЕНЬЕВ ЕГОР (Максим 1мф)</t>
+          <t>РОСКОСМОС</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>10-24958</t>
+          <t>5-33156</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>пн0001_1</t>
+          <t>пн0453_4</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Мягкие элементы /СУЛ/ Изделие №001 (14, 1924*1332*428 мм)</t>
+          <t>Кресло с полукруглой спинкой /ЧП/ Изделие № 0453 (07)</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>142500</v>
+        <v>23000</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>45820</v>
+        <v>45895</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ПАРФЕНЬЕВ ЕГОР (Максим 1мф)</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>11-24958</t>
+          <t>7-25078</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>пн0001_1</t>
+          <t>062</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Мягкие элементы /СУЛ/ Изделие №001 (15, 1924*1060*448 мм)</t>
+          <t>Кровать Siena Kids с креплением к стене 1120*2130*670 (900*2000)</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>118500</v>
+        <v>93340</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>45821</v>
+        <v>45888</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ПАРФЕНЬЕВ ЕГОР (Максим 1мф)</t>
+          <t>Коломяжский</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12-24958</t>
+          <t>1-33157</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>пн0001_1</t>
+          <t>пн0051_1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Мягкие элементы /СУЛ/ Изделие №001 (16, 480*4700*484 мм)</t>
+          <t>Услуги по перетяжке и обивке (58, изголовье (МЯГКАЯ ЧАСТЬ) 2600*80*1100 мм, Коломяжский)</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>110000</v>
+        <v>3800</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>45818</v>
+        <v>45896</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Серийная мебель</t>
+          <t>Коломяжский</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1-24974</t>
+          <t>2-33157</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>с-1697</t>
+          <t>пн0051_1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Евро-диван / "Монреаль" / База / (сп.м. 1,5x2,0 мм, полукруглый ш.подл. 130)</t>
+          <t>Услуги по перетяжке и обивке спринг бокса (59, 900*2000*h350 мм, высота борта - 250 мм, ножка - 100 мм Коломяжский)</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>39800</v>
+        <v>2150</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>45789</v>
+        <v>45896</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>РОСКОСМОС</t>
+          <t>Рыжий</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1-24975</t>
+          <t>1-33161</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>пн0453</t>
+          <t>пн603_13</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Диван трехместный НЕ раскладной /ЧП/ Изделие № 0453 (01, 2200*850*850 мм)</t>
+          <t>Услуги по реставрации левой части изголовья (63, вариант 1 (1150*2420 мм))</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>148000</v>
+        <v>3500</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>45791</v>
+        <v>45918</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>РОСКОСМОС</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2-24975</t>
+          <t>1-33165</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>пн0453</t>
+          <t>0119</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Кресло мягкое НЕ раскладное /ЧП/ Изделие № 0453 (02, 800*850*850 мм)</t>
+          <t>Кровать Siena kids стандартное Г образное  изголовье (СБОКУ) 1200*2000; 2120*1520*670h</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>72500</v>
+        <v>110000</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>45789</v>
+        <v>45918</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Елизавета Сапачук</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>РОСКОСМОС</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>4-24975</t>
+          <t>2-33165</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>пн0453</t>
+          <t>0119</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Диван двухместный НЕ раскладной /ЧП/ Изделие № 0453 (03, 1550*850*850 мм)</t>
+          <t>Банкетка к детской кровати Siena Kids (COMO) 1800*800*670</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>70000</v>
+        <v>31700</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>45790</v>
+        <v>45918</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Владислав Букин</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ярошевич</t>
+          <t>ВИП Старостенко</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1-24976</t>
+          <t>3-33167</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>пн946</t>
+          <t>пн0476</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Диван полукруглый /FP/ Изделие №0946 (02, 2500*1250*h800 мм)</t>
+          <t>Кровать детская с одним подлокотником /1мф/ Изделие № 0476 (03, 2056*998*h700 мм)</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>380000</v>
+        <v>66000</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>45825</v>
+        <v>45916</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Владислав Букин</t>
+          <t>Букин Владислав</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ярошевич</t>
+          <t>ВИП Старостенко</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2-24976</t>
+          <t>6-33167</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>пн946</t>
+          <t>пн0476</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Диван /FP/ Изделие №0946 (03)</t>
+          <t>Кровать детская с подлокотниками /1мф/ Изделие № 0476 (04, 2032*998*h700 мм)</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>260000</v>
+        <v>69000</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>45807</v>
+        <v>45917</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Елизавета Сапачук</t>
+          <t>Букин Владислав</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>УК Летниковка</t>
+          <t>Грибоедова (ДОРОС)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>4-24933</t>
+          <t>2-33168</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>пн0923</t>
+          <t>пн0062</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Услуги по ремонту (17, кресла)</t>
+          <t>Спринг бокс 1500*2000*h350 мм (высота борта 270 мм, ножка 80 мм)</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>18100</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>45787</v>
+        <v>45901</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ПРОРЫВ</t>
+          <t>Разовый заказ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1-24978</t>
+          <t>1-24919</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>пн0463</t>
+          <t>пн0003</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Стол большой текстурный /ЧП/ Изделие № 0463 (01, 2300*1100*750 мм)</t>
+          <t>Чехол подушки декоративной / Стандарт / С молнией / Изделие №0003 (01,550*400 мм</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>105000</v>
+        <v>1800</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>45820</v>
+        <v>45891</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ПРОРЫВ</t>
+          <t>Разовый заказ</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2-24978</t>
+          <t>3-24919</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>пн0463</t>
+          <t>пн0003</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Стол большой текстурный /ЧП/ Изделие № 0463 (02, 1500*800*750 мм)</t>
+          <t>Чехол подушки декоративной / Стандарт / С молнией / Изделие №0003 (02,650*600 мм)</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>78000</v>
+        <v>2300</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>45820</v>
+        <v>45891</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Сокольники</t>
+          <t>Разовый заказ</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>3-24927</t>
+          <t>4-24919</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>пн0050_1</t>
+          <t>пн0003</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Услуги по перетяжке и обивке (51, пуф)</t>
+          <t>Услуга по перетяжке и обивке стула (60)</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>45824</v>
+        <v>45891</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Елизавета Сапачук</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Сокольники</t>
+          <t>Разовый заказ</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>4-24927</t>
+          <t>1-25117</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>пн0050_1</t>
+          <t>пн113</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Пуф прямоугольный /СЗМК/ Изделие №0050 (04, 900*520*h450 мм)</t>
+          <t>Услуги по перетяжке и обивке (61, стул Двинцев)</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>45833</v>
+        <v>45891</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Елизавета Сапачук</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>COMO (КОМО)</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1-24979</t>
+          <t>1-33175</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>00113</t>
+          <t>240  - 351</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Кровать Siena Fly (COMO) стандартное (двойное) тонкое изголовье 2020х2330х670h (2000*2000)</t>
+          <t>Кресло для отдыха / "Мадрид" / (ш.подл. 100 мм. на деревянных опорах орех 170 мм)</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>123900</v>
+        <v>19090</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>45796</v>
+        <v>45895</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>COMO (КОМО)</t>
+          <t>Консульская деревня</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1-24980</t>
+          <t>6-24848</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>00114</t>
+          <t>пн445</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Кровать Siena (COMO) стандартное (одинарное) тонкое изголовье 2330*1820х670h (1600*2000 мм)</t>
+          <t>Услуги по перетяжке и обивке ( кресло Консульская деревня)</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102900</v>
+        <v>14000</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>45796</v>
+        <v>45896</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1мф частному лицу</t>
+          <t>Консульская деревня</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1-24982</t>
+          <t>7-24848</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>пн0473</t>
+          <t>пн445</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Сидушка (подбагажница) /1мф/ Изделие №0473 (01, 1130х400х60 мм)</t>
+          <t>Услуги по перетяжке и обивке ( пуфа Консульская деревня)</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>21000</v>
+        <v>4000</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>45805</v>
+        <v>45896</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ПРОРЫВ</t>
+          <t>Авенир Ладожский Дорос</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>4-24978</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>пн0463</t>
-        </is>
-      </c>
+          <t>1-33179</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Диван Sviwel Brice (1800*830*760 мм)</t>
+          <t>Услуга по перетяжке и обивке бокса 900*2000 мм Авенир Ладожский</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>120000</v>
+        <v>2550</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>45797</v>
+        <v>45896</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>YES на Марата</t>
+          <t>Рыжий</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1-24987</t>
+          <t>4-24997</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>пн0014Пилот</t>
+          <t>пн603_12</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Изголовье /СЗМК/ Изделие №0014 (01, 2670*1000 мм)</t>
+          <t>Ножка буковая для бокса (150 мм, без колеса)</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>19800</v>
+        <v>340</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>45806</v>
+        <v>45903</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ОЗОН</t>
+          <t>VIDI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1-24990</t>
+          <t>2-33184</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Озон-2</t>
+          <t>пн284_3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Спринг Бокс 1000*2000 мм</t>
+          <t>Ножка буковая для бокса (150 мм, с колесом)</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>12708</v>
+        <v>450</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>45800</v>
+        <v>45903</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ОЗОН</t>
+          <t>Евгения от Петракова</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1-24991</t>
+          <t>1-33192</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>озон-1</t>
+          <t>пн0484</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Спринг бокс 1000*1900 мм</t>
+          <t>Кресло /ЧП/ Изделие № 0484 (01)</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>12123</v>
+        <v>88000</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>45800</v>
+        <v>45906</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ОЗОН</t>
+          <t>Евгения от Петракова</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1-24995</t>
+          <t>2-33192</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>озон-3</t>
+          <t>пн0484</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Спринг бокс 800*2000</t>
+          <t>Кресло (зеркальное) /ЧП/ Изделие № 0484 (02)</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>11254</v>
+        <v>55000</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>45805</v>
+        <v>45904</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Подиумы</t>
+          <t>Разовый заказ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1-24992</t>
+          <t>1-33193</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>пн0958</t>
+          <t>пн485</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Подиум Швеция, ДУБ /FP/ (2105*1060*140 мм)</t>
+          <t>Услуги по перетяжке и обивке (62, кровать ОБП)</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>18600</v>
+        <v>12000</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>45804</v>
+        <v>45908</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Подиумы</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2-24992</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>пн0958</t>
-        </is>
-      </c>
+          <t>1-33200</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Подиум Швеция, ДУБ /FP/ (1770*1040*140 мм)</t>
+          <t>Услуги по перетяжке и обивке оттоманки дивана Монреаль 25069</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>17600</v>
+        <v>0</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>45804</v>
+        <v>45908</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Яндекс</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1-25003</t>
+          <t>1-33202</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Спринг бокс (1200*2000 мм)</t>
+          <t>Перетяжка оттоманки дивана Монреаль 24942</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>20438</v>
+        <v>0</v>
       </c>
       <c r="F96" s="1" t="n">
-        <v>45807</v>
+        <v>45908</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Владислав Букин</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Сокольники</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1-25004</t>
+          <t>1-33203</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>пн0489</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Евро-диван "Манчестер"  (сп.м 1500*2000), накл. венге</t>
+          <t>Зеркало d1500 мм</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>44200</v>
+        <v>29500</v>
       </c>
       <c r="F97" s="1" t="n">
-        <v>45811</v>
+        <v>45908</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Well Doros</t>
+          <t>Сергей Митхед</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1-25007</t>
+          <t>1-33204</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>пн106р</t>
+          <t>пн0493</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Услуги по перетяжке и обивке (52, сидушка дивана Well Вэлл)</t>
+          <t>Комплект (спинки и сидушка) /ЧП/ Изделие № 0493 (01)</t>
         </is>
       </c>
       <c r="E98" t="n">
         <v>6000</v>
       </c>
       <c r="F98" s="1" t="n">
-        <v>45807</v>
+        <v>45918</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Серийная мебель</t>
+          <t>YES на Марата</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1-25010</t>
+          <t>3-33205</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>С-1730</t>
+          <t>пн0014</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Евро-диван / "Монреаль" / База /Сп.м 1500*2000</t>
+          <t>Подушка подбагажника 689*538*65 мм</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>40600</v>
+        <v>4100</v>
       </c>
       <c r="F99" s="1" t="n">
-        <v>45811</v>
+        <v>45919</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Технопарк</t>
+          <t>Разовый заказ</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>4-25028</t>
+          <t>1-33207</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>пн0083_1</t>
+          <t>пн0490</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Журнальный столик /СЗМК/ Изделие № 0083 (04, д450*в600 мм)</t>
+          <t>Подбагажница /ЧП/ Изделие № 0490 (677*380*100 мм)</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>20160</v>
+        <v>3900</v>
       </c>
       <c r="F100" s="1" t="n">
-        <v>45825</v>
+        <v>45916</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Технопарк</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5-25028</t>
+          <t>1-33215</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>пн0083_1</t>
+          <t>0137</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Светодиодный светильник /СЗМК/ Изделие №0083 (05)</t>
+          <t>Пуф Bonbon 800*900*350 L</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>9600</v>
+        <v>14600</v>
       </c>
       <c r="F101" s="1" t="n">
-        <v>45825</v>
+        <v>45918</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Магазин СЗМК pro</t>
+          <t>Пригожин (личное)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1-25021</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>1-33222</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>110р</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Угловой диван / "Люксенбург угол" / База / (сп.м. 1,5x2,1 м, мягкий, ф. 7)</t>
+          <t>Пуговицы (желтые)</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F102" s="1" t="n">
-        <v>45825</v>
+        <v>45919</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Магазин СЗМК pro</t>
+          <t>Пригожин (личное)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2-25021</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>2-33222</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>110р</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Евро диван / "Пионер" / База / (сп.м. 2,0х1,5 м, подл. низкие)</t>
+          <t>Пуговицы (синие)</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F103" s="1" t="n">
-        <v>45820</v>
+        <v>45919</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Магазин СЗМК pro</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5-25021</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
+          <t>3-33223</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0133</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Кресло "LESLIE"</t>
+          <t>Кровать Siena Kids Г образная, с механизмом (1200*2000),  1820*2530*670</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>83000</v>
       </c>
       <c r="F104" s="1" t="n">
-        <v>45821</v>
+        <v>45930</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Елизавета Сапачук</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Магазин СЗМК pro</t>
+          <t>Евгения от Петракова</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>7-25021</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
+          <t>1-33226</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>пн0497</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Пуф "LESLIE"</t>
+          <t>Пуф круглый /ЧП/ Изделие № 0497 (01, 400*400*450 мм)</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="F105" s="1" t="n">
-        <v>45821</v>
+        <v>45919</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Елизавета Сапачук</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Ботаника</t>
+          <t>Евгения от Петракова</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1-24998</t>
+          <t>2-33226</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>пн0083</t>
+          <t>пн0497</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Кроватный бокс угловой /СЗМК/ Изделие № 0083 (01, 1600*2000 мм)</t>
+          <t>Чехол на подставку для сумок и хлястик /ЧП/ Изделие №0497 (02)</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>44352</v>
+        <v>1000</v>
       </c>
       <c r="F106" s="1" t="n">
-        <v>45819</v>
+        <v>45919</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Ботаника</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2-24998</t>
+          <t>1-33228</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>пн0083</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Спинка длинная /СЗМК/ Изделие № 0083 (02)</t>
+          <t>Евро-диван / "Монреаль" / База / (сп.м. 1,9х1,5 м, мягкий)</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="F107" s="1" t="n">
-        <v>45819</v>
+        <v>45919</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Ботаника</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>3-24998</t>
+          <t>1-33227</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>пн0083</t>
+          <t>240-367</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Спинка короткая /СЗМК/ Изделие № 0083 (03)</t>
+          <t>Угловой диван / "Монреаль" / База / (сп.м. 1,9х1,5 м, ф. 7, )</t>
         </is>
       </c>
       <c r="E108" t="n">
         <v>0</v>
       </c>
       <c r="F108" s="1" t="n">
-        <v>45819</v>
+        <v>45919</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Консульская деревня</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>3-24848</t>
+          <t>1-33232</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>пн445</t>
+          <t>122/1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Услуги по перетяжке и обивке (53, углового дивана Консульская деревня)</t>
+          <t>Кровать Siena kids(como) с тонким L образным изголовьем, с подъемным механизмом (1200*2000), 1620*330*670)</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>83000</v>
       </c>
       <c r="F109" s="1" t="n">
-        <v>45825</v>
+        <v>45919</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Консульская деревня</t>
+          <t>УЛЬТРАМАР</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>4-24848</t>
+          <t>4-33234</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>пн445</t>
+          <t>пн0476</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Услуги по перетяжке и обивке (54, большого П-образного дивана Консульская деревня)</t>
+          <t>Стол полубарный LATOS 3 /ЧП/ Изделие № 0476 (04, 1800*600*920 мм)</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>90376</v>
       </c>
       <c r="F110" s="1" t="n">
-        <v>45825</v>
+        <v>45922</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Консульская деревня</t>
+          <t>УЛЬТРАМАР</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5-24848</t>
+          <t>5-33234</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>пн445</t>
+          <t>пн0476</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Услуги по реставрации (08, стол Консульская деревня)</t>
+          <t>Стол обеденный LATOS 1 /ЧП/ Изделие № 0476 (05, 1400*800*750 мм)</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>74800</v>
       </c>
       <c r="F111" s="1" t="n">
-        <v>45825</v>
+        <v>45922</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Разовый заказ</t>
+          <t>УЛЬТРАМАР</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1-25033</t>
+          <t>6-33234</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>пн0480</t>
+          <t>пн0476</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Мягкий элемент /1мф/ Изделие №0480 (01, 1080х400х60 мм)</t>
+          <t>Стол обеденный LATOS 2 /ЧП/ Изделие № 0476 (05, 2200*800*750 мм)</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>20200</v>
+        <v>98560</v>
       </c>
       <c r="F112" s="1" t="n">
-        <v>45833</v>
+        <v>45922</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Сокольники</t>
+          <t>ИКС-Холдинг</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1-25037</t>
+          <t>2-33236</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>пн0050_2</t>
+          <t>пн0494</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Услуги по доработке звуковых панелей (03, панель Сокольники)</t>
+          <t>Пуф прямоугольный /ЧП/ Изделие № 0494 (02, 600*400*450 мм)</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="F113" s="1" t="n">
-        <v>45826</v>
+        <v>45924</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Коломяжский</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1-25019</t>
+          <t>4-33223</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>пн0051</t>
+          <t>0133</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Изголовье (МЯГКАЯ ЧАСТЬ) /СЗМК/ Изделие №0051 (01, 2600*80*1100 мм)</t>
+          <t>Кровать Siena Kids L образная,без механизма 1200*2000 (1200*2000 мм, 1820*2530*670)</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>20200</v>
+        <v>83000</v>
       </c>
       <c r="F114" s="1" t="n">
-        <v>45835</v>
+        <v>45924</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Коломяжский</t>
+          <t>ПЕРВЫЙ</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2-25019</t>
+          <t>1-33209</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>пн0051</t>
+          <t>пн0487</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Спринг бокс /СЗМК/ Изделие №0051 (02, 900*2000*h350 мм) высота борта - 250 мм, ножка - 100 мм</t>
+          <t>Подушка двухсторонняя с утяжками, БЕЗ пуговиц /ЧП/ Изделие № 0487 (01, 300*600 мм)</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>15200</v>
+        <v>3789.66</v>
       </c>
       <c r="F115" s="1" t="n">
-        <v>45833</v>
+        <v>45930</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Серийная мебель</t>
+          <t>Разовый заказ</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1-25049</t>
+          <t>1-33244</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>В Зал</t>
+          <t>пн0498</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Евро-диван / "Монреаль" / База / (сп.м. 2,0х1,5, ящ. с накл.)</t>
+          <t>Спинка + сидушка (комплект) /ЧП/ Изделие № 0498 (01)</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>39800</v>
+        <v>0</v>
       </c>
       <c r="F116" s="1" t="n">
-        <v>45833</v>
+        <v>45930</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Серийная мебель</t>
+          <t>Разовый заказ</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1-25051</t>
+          <t>1-33246</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Магазин</t>
+          <t>пн0129</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Угловой диван / "Люксенбург угол" / База /</t>
+          <t>Реставрация кресла (01)</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>70000</v>
+        <v>5800</v>
       </c>
       <c r="F117" s="1" t="n">
-        <v>45833</v>
+        <v>45930</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Грибоедова (1МФ)</t>
+          <t>Разовый заказ</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>4-25039</t>
+          <t>2-33246</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>пн0465_1</t>
+          <t>пн0129</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Кресло без поворотного механизма /1мф/ Изделие №0451 (02)</t>
+          <t>Реставрация барный стул (02)</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>32500</v>
+        <v>0</v>
       </c>
       <c r="F118" s="1" t="n">
-        <v>45835</v>
+        <v>45930</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Дмитрий Харченко</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Грибоедова (ДОРОС)</t>
+          <t>Разовый заказ</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1-25060</t>
+          <t>3-33246</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>пн0062Пилот2</t>
+          <t>пн0129</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Услуги по перетяжке и обивке (55, спринг бокс 900*2000 Грибоедова Дорос)</t>
+          <t>Реставрация пуф (03)</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="F119" s="1" t="n">
-        <v>45834</v>
+        <v>45930</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Грибоедова (ДОРОС)</t>
+          <t>Разовый заказ</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2-25060</t>
+          <t>4-33246</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>пн0062Пилот2</t>
+          <t>пн0129</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Услуги по перетяжке и обивке (56, мягкие элементы Грибоедова Дорос)</t>
+          <t>Реставрация кресло Дайтвердер (03)</t>
         </is>
       </c>
       <c r="E120" t="n">
         <v>0</v>
       </c>
       <c r="F120" s="1" t="n">
-        <v>45834</v>
+        <v>45930</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Илья Харьков</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Грибоедова (ДОРОС)</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>3-25060</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>пн0062Пилот2</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Кресло без поворотного механизма Грибоедова Дорос (02, 760*740*h670 мм)</t>
-        </is>
-      </c>
-      <c r="E121" t="n">
-        <v>26500</v>
-      </c>
-      <c r="F121" s="1" t="n">
-        <v>45835</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Илья Харьков</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>ПАРФЕНЬЕВ ЕГОР (Максим 1мф)</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>1-25057</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>пн0001_2</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Экран разделительный /СУЛ/ Изделие №0001 (17, 1940*450*16 мм)</t>
-        </is>
-      </c>
-      <c r="E122" t="n">
-        <v>8800</v>
-      </c>
-      <c r="F122" s="1" t="n">
-        <v>45834</v>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>Илья Харьков</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>ПАРФЕНЬЕВ ЕГОР (Максим 1мф)</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>2-25057</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>пн0001_2</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Мягкие элементы /СУЛ/ Изделие №001 (18, 1895*1035*400 мм)</t>
-        </is>
-      </c>
-      <c r="E123" t="n">
-        <v>68000</v>
-      </c>
-      <c r="F123" s="1" t="n">
-        <v>45834</v>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Илья Харьков</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>

--- a/django_app/constructing_report.xlsx
+++ b/django_app/constructing_report.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,29 +459,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Производственный холдинг</t>
+          <t>ВАЛА</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5-24571</t>
+          <t>3-24423</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>чп347_1</t>
+          <t>пн81р</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Диван радиусный без скоса /ЧП/ Изделие №347 (06, 1100)</t>
+          <t>Услуги по перетяжке и обивке (№ 27, кресло Лемо)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>38250</v>
+        <v>3375</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>45868</v>
+        <v>45931</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -492,161 +492,161 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Производственный холдинг</t>
+          <t>Разовый заказ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6-24571</t>
+          <t>3-24792</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>чп347_1</t>
+          <t>пн386</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Диван радиусный без скоса /ЧП/ Изделие №347 (07, 1100)</t>
+          <t>Накладки на фасады для тумб /ЧП/ Изделие № 386 (03)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>38250</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>45876</v>
+        <v>45968</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Харьков Илья</t>
+          <t>ОКК Хвосты</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Производственный холдинг</t>
+          <t>ВАРШАВКА В4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7-24571</t>
+          <t>3-25000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>чп347_1</t>
+          <t>пн0917</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Диван радиусный со скосом /ЧП/ Изделие №347 (08, 1190)</t>
+          <t>Диван двухместный /FP/ Изделие № 0917 (03, дл 2480 мм)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42300</v>
+        <v>98000</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45868</v>
+        <v>45954</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Харьков Илья</t>
+          <t>Букин Владислав</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Производственный холдинг</t>
+          <t>ВАРШАВКА В4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8-24571</t>
+          <t>4-25000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>чп347_1</t>
+          <t>пн0917</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Диван радиусный со скосом /ЧП/ Изделие №347 (09, 1190)</t>
+          <t>Панель за стойкой /FP/ Изделие № 0917 (04)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>42300</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>45876</v>
+        <v>46012</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Харьков Илья</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Сокольники</t>
+          <t>ВАРШАВКА В4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2-24872</t>
+          <t>5-25000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>пн0050</t>
+          <t>пн0917</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Кровать реплика "ALYS 207-212-H92" / FP / Изделие №572_5322 / (16)</t>
+          <t>Подушка декоративная большая /FP/ Изделие № 0917 (05)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>280000</v>
+        <v>3597.2</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>45841</v>
+        <v>45931</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Харченко Дмитрий</t>
+          <t>Букин Владислав</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Сокольники</t>
+          <t>ВАРШАВКА В4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4-24872</t>
+          <t>6-25000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>пн0050</t>
+          <t>пн0917</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Кровать реплика Calligaris MIES MIX /СЗМК/ Изделие №0050 (01, под матрас 1400*2000 мм)</t>
+          <t>Подушка декоративная маленькая /FP/ Изделие № 0917 (06)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>150000</v>
+        <v>2597.2</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>45868</v>
+        <v>45931</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -657,161 +657,149 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Сокольники</t>
+          <t>Завьялов</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6-24872</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>пн0050</t>
-        </is>
-      </c>
+          <t>1-25107</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Кровать /СЗМК/ Изделие №0050 (03, под матрас 1400х2000 мм)</t>
+          <t>Диван "Бумеранг "</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>128000</v>
+        <v>393033.12</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>45852</v>
+        <v>45966</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Сапачук Елизавета</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Евгения от Петракова</t>
+          <t>Завьялов</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1-24936</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>пн459</t>
-        </is>
-      </c>
+          <t>2-25107</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Пуф /ЧП/ Изделия №0459 (01)</t>
+          <t>Декоративная подушка 370*370</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48550</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>45839</v>
+        <v>45971</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Сапачук Елизавета</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Евгения от Петракова</t>
+          <t>Завьялов</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2-24936</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>пн459</t>
-        </is>
-      </c>
+          <t>3-25107</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Кресло /ЧП/ Изделия №0459 (02)</t>
+          <t>Стол МДФ</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>74650</v>
+        <v>30000</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>45868</v>
+        <v>45974</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Сапачук Елизавета</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Летниковка</t>
+          <t>РОСКОСМОС</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20-23925</t>
+          <t>7-33156</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>пн663</t>
+          <t>пн0453_4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Стол реплика Studio Twentyseven (Стол Eros) /FP/ Изделие №663 (16,1800*450*h720 мм)</t>
+          <t>Кресло /ЧП/ Изделие № 0453 (08)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>380000</v>
+        <v>60000</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>45919</v>
+        <v>45984</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Харьков Илья</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UNO</t>
+          <t>РОСКОСМОС</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9-23815</t>
+          <t>8-33156</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>пн599_5959</t>
+          <t>пн0453_4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Кровать /FP/ Изделие №599 (Вариант №6)</t>
+          <t>Кресло /ЧП/ Изделие №0453 (09, 1100*800 мм)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>40800</v>
+        <v>85000</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>45887</v>
+        <v>45938</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -822,29 +810,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UNO</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23-23815</t>
+          <t>1-33166</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>пн599_5959</t>
+          <t>20009</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Кровать /FP/ Изделие №599 (Вариант №10)</t>
+          <t>Кровать Siena kids(como) с П образным изголовьем,900*2000, 2330*1300*670</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>40100</v>
+        <v>88000</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>45887</v>
+        <v>45952</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -855,29 +843,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UNO</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>24-23815</t>
+          <t>1-33164</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>пн599_5959</t>
+          <t>00132</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Кровать /FP/ Изделие №599 (Вариант №11)</t>
+          <t>Кровать Siena kids(como) с тонким 7 образным изголовьем, с подъемным механизмом СБОКУ(1200*2000), 1520*2330*350)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>40100</v>
+        <v>108000</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>45883</v>
+        <v>45943</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -888,29 +876,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UNO</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>25-23815</t>
+          <t>2-33164</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>пн599_5959</t>
+          <t>00132</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Кровать /FP/ Изделие №599 (Вариант №12)</t>
+          <t>Банкетка к детской кровати Siena Kids (COMO)  1520*800*350</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>41700</v>
+        <v>30000</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>45887</v>
+        <v>45945</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -921,58 +909,62 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UNO</t>
+          <t>ВИП Старостенко</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>26-23815</t>
+          <t>1-33167</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>пн599_5959</t>
+          <t>пн0476</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Кровать /FP/ Изделие №599 (Вариант №13)</t>
+          <t>Кровать /1мф/ Изделие № 0476 (01, 2066*1708 мм, сп.м. 1600*2000 мм)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>40100</v>
+        <v>72000</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>45883</v>
+        <v>45940</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Харьков Илья</t>
+          <t>Букин Владислав</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UNO</t>
+          <t>ВИП Старостенко</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1-24023</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>2-33167</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>пн0476</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Кушетка /FP/ Изделие №599_5959 (04, 1940*840*300 мм)</t>
+          <t>Изголовье (мягкий элемент) /1мф/ Изделие № 0476 (02, ш1654*в1901 мм)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>25900</v>
+        <v>89000</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>45919</v>
+        <v>45943</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -983,95 +975,91 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mercure Алтай</t>
+          <t>Завьялов</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1-24999</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>пн777_2Пилот</t>
-        </is>
-      </c>
+          <t>4-25107</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Изголовье (Мягкий элемент) /FP/ Изделие №777 (05, 3400*2300 мм)</t>
+          <t>Пуф круглый d100 h 450</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>43900</v>
+        <v>36900</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>45855</v>
+        <v>45978</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Букин Владислав</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mercure Алтай</t>
+          <t>Сергей Митхед</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2-24999</t>
+          <t>2-33204</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>пн777_2Пилот</t>
+          <t>пн0493</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Основание /FP/ Изделие №777 (06, 2000*2000 мм)</t>
+          <t>Диван эркерный /ЧП/ Изделие № 0493 (02)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>33300</v>
+        <v>190000</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>45866</v>
+        <v>45938</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Сапачук Елизавета</t>
+          <t>Букин Владислав</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mercure Алтай</t>
+          <t>Саша Югай</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3-24999</t>
+          <t>1-33208</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>пн777_2Пилот</t>
+          <t>пн003</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Диван с одним локтем /FP/ Изделие №777 (07, 1950*900*h920 мм)</t>
+          <t>Диван MONS /ЮГ/ Изделие № 003 (01, 1420*1020*h900 мм)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>59500</v>
+        <v>95000</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>45868</v>
+        <v>45943</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1082,62 +1070,62 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Туник Ульяна</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1-25029</t>
+          <t>2-33223</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>пн0408</t>
+          <t>0133</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Стул обеденный Fn-1 /ЧП/ Изделие №0408 (01)</t>
+          <t>Банкетка со спинкой   к  детской кровати Siena Kids ( 1820*800*200)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>42968.75</v>
+        <v>30000</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>45859</v>
+        <v>45931</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Харченко Дмитрий</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Туник Ульяна</t>
+          <t>Дорвэй</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2-25029</t>
+          <t>1-33225</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>пн0408</t>
+          <t>пн0488Пилот</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Стул Fn-16 /ЧП/ Изделие №0408 (02)</t>
+          <t>Стул с латунными наконечниками /ЧП/ Изделие № 0488 (01)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>42875</v>
+        <v>119200</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>45868</v>
+        <v>45956</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1148,62 +1136,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Авенир Ладожский 1МФ</t>
+          <t>Разовый заказ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4-25034</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>пн353_5</t>
-        </is>
-      </c>
+          <t>1-33239</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Изголовье /1мф/ Изделие №353  (03, 2110*50*h1030 мм с БРУСКАМИ)</t>
+          <t>Диван прямой изделие № 495 (2600*900)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>22900</v>
+        <v>125000</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>45868</v>
+        <v>45951</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Харьков Илья</t>
+          <t>Букин Владислав</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Серийная мебель</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1-25041</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>3810</t>
-        </is>
-      </c>
+          <t>1-33233</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Евро-диван / "Манчестер" / База / (сп.м. 1500*2000, накладки шимо)</t>
+          <t>Кровать "Практик" (сп.м 1800*2000мм, выс.бортов 400, выс.изголовья 1000)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>44200</v>
+        <v>25000</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>45841</v>
+        <v>45943</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1214,161 +1190,157 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Марриотт</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1-25032</t>
+          <t>3-33165</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>пн595_2</t>
+          <t>0119</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Изголовье / FP / Изделие №595 (01, 1900*1500 мм)</t>
+          <t>Банкетка со спинкой  - 1800 * 1320 * 670 мм</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>46850</v>
+        <v>0</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>45852</v>
+        <v>45931</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Сапачук Елизавета</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Грибоедова (1МФ)</t>
+          <t>RBI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3-25039</t>
+          <t>1-33247</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>пн0465_1</t>
+          <t>пн111р</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Пуф Грибоедов /1мф/ Изделие № 0451 (01, 800-900*h450 мм)</t>
+          <t>Реставрация стула Цыпленок (04)</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>12800</v>
+        <v>6400</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>45839</v>
+        <v>45943</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Сапачук Елизавета</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Грибоедова (ДОРОС)</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4-25060</t>
+          <t>1-33245</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>пн0062Пилот2</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Банкетка Грибоедов Дорос (03, 800*500*h450 мм)</t>
+          <t>Пуф Круглый 45см*45h</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>12100</v>
+        <v>9500</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>45839</v>
+        <v>45943</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Сапачук Елизавета</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Подиумы</t>
+          <t>Разовый заказ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1-25058</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>пн959</t>
-        </is>
-      </c>
+          <t>2-33239</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Подиум Швеция, ДУБ /FP/ (1590*670*210 мм)</t>
+          <t>пуф 700*700</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>17100</v>
+        <v>25000</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>45840</v>
+        <v>45959</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Харьков Илья</t>
+          <t>Букин Владислав</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Рыжий</t>
+          <t>Well Doros</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2-24925</t>
+          <t>1-33255</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>пн104р</t>
+          <t>пн112р</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Услуги по перетяжке и обивке (57, бокс 1000*2000*350 мм, ВАЛА)</t>
+          <t>Сидушка дивана Велл (Well)</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2550</v>
+        <v>0</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>45847</v>
+        <v>45939</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1379,29 +1351,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Серийная мебель</t>
+          <t>Well Doros</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1-25075</t>
+          <t>2-33255</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>С-1760</t>
+          <t>пн112р</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Угловой диван / "Монреаль" / База / (сп.м. 1,9х1,5 м, ф. Г, мягкий)</t>
+          <t>Короб дивана Велл (Well)</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>48400</v>
+        <v>0</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>45841</v>
+        <v>45939</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1412,29 +1384,29 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COMO (КОМО)</t>
+          <t>ВАЛА</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1-25076</t>
+          <t>1-33256</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>пн113р</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Кровать Siena стандартное (одинарное) тонкое изголовье с подъемным механизмом 2330*1620х670h (1400*2000 мм)</t>
+          <t>Реставрация уха панели К5 (ВАЛА)</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>92500</v>
+        <v>3200</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>45855</v>
+        <v>45939</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1445,62 +1417,62 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Серийная мебель</t>
+          <t>Громово</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1-25077</t>
+          <t>1-33257</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>С-1761</t>
+          <t>пн0130</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Минитахта / "Прага" / База / (ш. 1,8 м)</t>
+          <t>Банкетка /СЗМК/ Изделие № 0130 (01, 900*450*450 мм)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>30100</v>
+        <v>15000</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>45853</v>
+        <v>45958</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Харьков Илья</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Наталья Мебель Маркет СПБ</t>
+          <t>Громово</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1-25045</t>
+          <t>2-33257</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>пн0002</t>
+          <t>пн0130</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Евро-диван / "Монреаль" / База / (сп.м. 1,9х1,5 м, ш.подл. 70 мм)</t>
+          <t>Стул Mad Diwing (Мэд Дайвинг) /СЗМК/ Изделие № 0130 (02)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>115200</v>
+        <v>29000</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>45847</v>
+        <v>45940</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1511,29 +1483,29 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Наталья Мебель Маркет СПБ</t>
+          <t>Громово</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2-25045</t>
+          <t>3-33257</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>пн0002</t>
+          <t>пн0130</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Кресло /СУЛ/ Изделие №0001 (02, 750*750*h805 мм)</t>
+          <t>Реставрация стула Mad Diwing (Мэд Дайвинг)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>39200</v>
+        <v>29000</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>45847</v>
+        <v>45939</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1542,60 +1514,64 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Громово</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1-25083</t>
+          <t>5-33257</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Рекламация</t>
+          <t>пн0130</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Услуги по перетяжке и обивке диван "Люксембург"</t>
+          <t>Реставрация дивана Rooma design Mark /СЗМК/ Изделие № 03 (2800*2200*H850 мм)</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>45847</v>
+        <v>45944</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Харьков Илья</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Подиумы</t>
+          <t>Громово</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1-25085</t>
+          <t>6-33257</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>пн960</t>
+          <t>пн0130</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Подиум Белпорт, дуб /FP/ Изделие № 960 (01, 1580*480*150 мм)</t>
+          <t>Диван компаньон Rooma design Mark /СЗМК/ Изделие № 0130 (04, 2000*950*H850 мм)</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>145000</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>45855</v>
+        <v>45954</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1606,29 +1582,29 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Наталья Мебель Маркет СПБ</t>
+          <t>Громово</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1-25093</t>
+          <t>7-33257</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>пн0012</t>
+          <t>пн0130</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Диван не раскладной /СУЛ/ Изделие №0012 (01, 2700* 900*H 840 мм)</t>
+          <t>Реставрация кресла Sits Blackbird</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>104345.78</v>
+        <v>15000</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>45868</v>
+        <v>45939</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1639,29 +1615,29 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Наталья Мебель Маркет СПБ</t>
+          <t>Громово</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2-25093</t>
+          <t>8-33257</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>пн0012</t>
+          <t>пн0130</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Кровать /ЧП/ Изделие №121 (09, 1800*2100 мм)</t>
+          <t>Реставрация подставка для ног Sits Blackbird</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>55126.07</v>
+        <v>0</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>45868</v>
+        <v>45939</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1672,29 +1648,29 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Наталья Мебель Маркет СПБ</t>
+          <t>Громово</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3-25093</t>
+          <t>10-33257</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>пн0012</t>
+          <t>пн0130</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Кресло /ЧП/ Изделие №121 (02, 1100*900 мм)</t>
+          <t>Сидушка /СЗМК/ Изделие № 0130 (05, 800*400*60-70мм)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>68907.59</v>
+        <v>4500</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>45868</v>
+        <v>45979</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1705,29 +1681,29 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>COMO (КОМО)</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6-25078</t>
+          <t>2-33224</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>062</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Кровать Siena fly  с креплением к стене без панелей 2220*2530*670 (1800*2000)</t>
+          <t>Подушки малые к дивану /nov/ Изделие №06 (03)</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>98000</v>
+        <v>0</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>45884</v>
+        <v>45947</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1736,23 +1712,31 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Социалистиеская/Yes</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1-25105</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>1-33263</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>пн0489</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Изголовье для кровати 2190*30*900</t>
+          <t>Спринг бокс /1мф/ Изделие № 0489 (01, 900*2000*300 мм с перфорацией в верхней части каркаса, царга - 220 мм, опора - 80 мм)</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>15000</v>
+        <v>13800</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>45895</v>
+        <v>45946</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1763,29 +1747,29 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>COMO (КОМО)</t>
+          <t>Социалистиеская/Yes</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1-25095</t>
+          <t>2-33263</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0130</t>
+          <t>пн0489</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Основание детской кровати Siena Kids с Тонким  П образным изголовьем (1110*2330*h670мм, 900*2000 мм)</t>
+          <t>Изголовье /1мф/ Изделие № 0489 (02, 2670*1000 мм)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>88000</v>
+        <v>21000</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>45860</v>
+        <v>45950</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1796,29 +1780,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>COMO (КОМО)</t>
+          <t>Социалистиеская/Yes</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1-25099</t>
+          <t>3-33263</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>00120</t>
+          <t>пн0489</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Кровать Siena(основание из 2 частей), увеличенное тонкое одинарное изг. (2820*2330*670_) 2000*2000</t>
+          <t>Подбагажница /1мф/ Изделие № 0489 (03, 768*500*60 мм)</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>123000</v>
+        <v>4900</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>45877</v>
+        <v>45947</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1829,29 +1813,29 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>COMO (КОМО)</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1-25106</t>
+          <t>1-33265</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0124</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Модуль FLAT Classic 1600*1000*400 опоры Массив</t>
+          <t>Евро-диван / "Манчестер" / База / (сп.м. 2,0х1,5 м, мягкий)</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53000</v>
+        <v>43440</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>45894</v>
+        <v>45945</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1867,24 +1851,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1-25102</t>
+          <t>1-33273</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>00122</t>
+          <t>00139</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Кровать Siena Fly (COMO) стандартное одинарное тонкое изголовье 2020х2330х670h  ( 1800*2000)</t>
+          <t>Модуль FLAT Classic 1800*1200*400 опоры Массив</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>98000</v>
+        <v>99575</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>45882</v>
+        <v>45951</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1895,29 +1879,29 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>COMO (КОМО)</t>
+          <t>ВИП Гурнович</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4-25102</t>
+          <t>1-33279</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>00122</t>
+          <t>пн0494</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Модуль FLAT 2000*1000*400 опоры Slot</t>
+          <t>Подбагажница /1мф/ Изделие № 0494 (01, 685*450*50 мм)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>57000</v>
+        <v>4100</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>45876</v>
+        <v>45953</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1928,29 +1912,29 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>COMO (КОМО)</t>
+          <t>ВИП Гурнович</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10-25102</t>
+          <t>2-33279</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>00122</t>
+          <t>пн0494</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Кровать Siena kids(como) с тонким Г образным изголовьем, с подъемным механизмом (1200*2000), 1620*330*670)</t>
+          <t>Подбагажница /1мф/ Изделие № 0494 (02, 585*550*50 мм)</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>83000</v>
+        <v>4200</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>45898</v>
+        <v>45953</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1961,29 +1945,29 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Гостиница Чечня</t>
+          <t>Mercure Алтай</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1-25110</t>
+          <t>1-33283</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>пн 0085</t>
+          <t>пн0777</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Спринг бокс /СЗМК/ Изделие №0085 (01, 800*2000*h350 мм) высота борта - 250 мм, ножка - 100 мм</t>
+          <t>Изголовье (Мягкий элемент) /FP/ Изделие №777 (08, 3400*2200 мм)</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>16400</v>
+        <v>43900</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>45860</v>
+        <v>45980</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1994,29 +1978,29 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Гостиница Чечня</t>
+          <t>Mercure Алтай</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2-25110</t>
+          <t>3-33283</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>пн 0085</t>
+          <t>пн0777</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Изголовье (мягкий элемент) /СЗМК/ Изделие №0085 (02, 1200*1900*толщ50 мм)</t>
+          <t>Бокс /FP/ Изделие № 0777 (09, 2000*2000*h250борта, ножка 100 мм)</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>16100</v>
+        <v>33500</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>45860</v>
+        <v>45954</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2027,29 +2011,29 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Разовый заказ</t>
+          <t>Mercure Алтай</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1-25112</t>
+          <t>4-33283</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>пн0484</t>
+          <t>пн0777</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Мягкий элемент /1мф/ Изделие №0484 (01, 1203х400х60 мм)</t>
+          <t>Диван с одним локтем /FP/ Изделие №777 (10, 1950*900*h900 мм, Ф7)</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>22400</v>
+        <v>59500</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>45888</v>
+        <v>45954</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2060,29 +2044,29 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Завидово</t>
+          <t>Тендер (РОДИНА)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1-25114</t>
+          <t>1-33277</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>пн0475</t>
+          <t>пн 0359</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Подбагажница /1мф/ Изделие № 0475 (01, 800*536*40 мм)</t>
+          <t>Диван раскладной индивидуального изготовления /SM/ Изделие № 0359 (01)</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6300</v>
+        <v>69000</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>45870</v>
+        <v>45989</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2093,29 +2077,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Статио Проджект</t>
+          <t>Тендер (РОДИНА)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1-25094</t>
+          <t>2-33277</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>пн0366</t>
+          <t>пн 0359</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Пуф /СМ/ Изделие №0366 (01, d450*h500 мм)</t>
+          <t>Комплект чехлов на подушки и подлокотники для дивана /SM/ Изделие № 0359 (02)</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6650</v>
+        <v>10000</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>45868</v>
+        <v>45974</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2126,91 +2110,95 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Магазин СЗМК pro</t>
+          <t>Тендер (РОДИНА)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2-25021</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>3-33277</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>пн 0359</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Евро диван / "Пионер" / База / (сп.м. 1,9х1,5 м, подл. низкие)</t>
+          <t>Кресло индивидуального изготовления /SM/ Изделие № 0359 (03)</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>33900</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>45869</v>
+        <v>45986</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>СЗМК Админ</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kempinsky Erevan</t>
+          <t>Тендер (РОДИНА)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1-33133</t>
+          <t>4-33277</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>пн0012</t>
+          <t>пн 0359</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Стул Kempinski /NOV/ Изделие №0012 (01)</t>
+          <t>Комплект чехлов на подушки и подлокотники для кресла /SM/ Изделие № 0359 (04)</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>45883</v>
+        <v>45974</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Харченко Дмитрий</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Грибоедова (ДОРОС)</t>
+          <t>Тендер (РОДИНА)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1-33135</t>
+          <t>5-33277</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>пн0115</t>
+          <t>пн 0359</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ножка дубовая Грибоедово /СЗМК/ Изделие №0115 (01, 650*90*30 мм)</t>
+          <t>Пуф индивидуального изготовления /SM/ Изделие № 0359 (05, 600*600*h480 мм)</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2500</v>
+        <v>10900</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>45876</v>
+        <v>45985</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2221,62 +2209,62 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Архыз</t>
+          <t>Тендер (РОДИНА)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1-33139</t>
+          <t>6-33277</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>пн0477</t>
+          <t>пн 0359</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Основание /1мф/ Изделие № 0477 (01, 2000*1000 мм)</t>
+          <t>Чехол на подушку для пуфа /SM/ Изделие № 0359 (064)</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>16500</v>
+        <v>2800</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>45876</v>
+        <v>45974</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Харченко Дмитрий</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Архыз</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2-33139</t>
+          <t>8-25118</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>пн0477</t>
+          <t>0086</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Изголовье /1мф/ Изделие № 0477 (02, 1000*1000 мм)</t>
+          <t>Подушка(сидушка)  590х570х150мм</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>9400</v>
+        <v>3500</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>45882</v>
+        <v>45952</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2287,190 +2275,194 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Архыз</t>
+          <t>Well Doros</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3-33139</t>
+          <t>1-33285</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>пн0477</t>
+          <t>пн695_20</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Пуф /1мф/ Изделие № 0477 (03, 450*400*350 мм)</t>
+          <t>Диван WELL нестандарт /FP/ Изделие №695 (23, 2100 мм локти 150 мм)</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>23000</v>
+        <v>66000</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>45883</v>
+        <v>45980</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Харченко Дмитрий</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Разовый заказ</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1-33142</t>
+          <t>1-33286</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>пн0483</t>
+          <t>0142</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Мягкий элемент /1мф/ Изделие № 0483 (01,1600 х 450 х h450 мм)</t>
+          <t>Кровать Siena  Стандарт. одинарное тонкое изголовье 2020*2330*820(1800x2000) c подъемным механизмом</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>25000</v>
+        <v>98000</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>45888</v>
+        <v>45958</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Букин Владислав</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Маркет плейсы</t>
+          <t>Mercure Алтай</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1-33143</t>
+          <t>5-33283</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>пн0777</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Спринг бокс 1200*1900</t>
+          <t>Диван с одним локтем /FP/ Изделие №777 (10, 1950*900*h900 мм, ФГ)</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>20400</v>
+        <v>59500</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>45877</v>
+        <v>45957</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Букин Владислав</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Серийная мебель</t>
+          <t>УЛЬТРАМАР</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2-33144</t>
+          <t>1-33234</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>пн0476</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Подушка к дивану Люксембург</t>
+          <t>Стул-кресло CONCORDЕ 1/ЧП/ Изделие № 0476 (02,558*545*818 мм)</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>23567.65</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>45888</v>
+        <v>46006</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Харьков Илья</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Серийная мебель</t>
+          <t>УЛЬТРАМАР</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1-33149</t>
+          <t>2-33234</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>В зал</t>
+          <t>пн0476</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Евро-диван / "Манчестер" / База / (сп.м. 2,0х1,5 м, стол)</t>
+          <t>Стол обеденный VERSO /ЧП/ Изделие № 0476 (03, d110*в750 мм, опора: d основ.650 мм)</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>47900</v>
+        <v>47969.55</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>45882</v>
+        <v>45986</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Харьков Илья</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Серийная мебель</t>
+          <t>Подиумы</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1-33150</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>1-33287</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>пн</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Перетяжка углового дивана Монреаль</t>
+          <t>Подиум Швеция, ДУБ /FP/ (1955*1060*140 мм)</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>19600</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>45882</v>
+        <v>45958</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2481,29 +2473,29 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Грибоедова (ДОРОС)</t>
+          <t>Подиумы</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1-33152</t>
+          <t>2-33287</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>пн0115_1</t>
+          <t>пн</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Услуги по перекраске ножки дубовой Грибоедово /СЗМК/ Изделие №0115 (01, 650*90*30 мм)</t>
+          <t>Подиум Швеция, ДУБ /FP/ (2450*1060*140 мм)</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1300</v>
+        <v>23800</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>45883</v>
+        <v>45958</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2514,29 +2506,29 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Завидово</t>
+          <t>Подиумы</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1-33146</t>
+          <t>1-33289</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>пн0475_1</t>
+          <t>пн967</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Спринг бокс (900*2000 мм) с усиленной фиксацией</t>
+          <t>Подиум под Швецию, ДУБ /FP/ (2650*1060*140 мм)</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>13300</v>
+        <v>26100</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>45882</v>
+        <v>45958</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2547,29 +2539,29 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Завидово</t>
+          <t>Подиумы</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2-33146</t>
+          <t>2-33289</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>пн0475_1</t>
+          <t>пн967</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Изголовье /1мф/ Изделие № 0475 (02, ш900*в883 мм) с креплением к боксу</t>
+          <t>Подиум под Швецию, ДУБ /FP/ (1070*1070*140 мм)</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>9100</v>
+        <v>16100</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>45882</v>
+        <v>45958</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2580,29 +2572,29 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Завидово</t>
+          <t>Подиумы</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>4-33146</t>
+          <t>1-33293</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>пн0475_1</t>
+          <t>пн968</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Изголовье /1мф/ Изделие № 0475 (03, ш1800*в883 мм)</t>
+          <t>Подиум Швеция, ДУБ /FP/ (1710*1060*140 мм)</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>16900</v>
+        <v>18900</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>45882</v>
+        <v>45959</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2613,29 +2605,29 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Завидово</t>
+          <t>Подиумы</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>6-33146</t>
+          <t>2-33293</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>пн0475_1</t>
+          <t>пн968</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Изголовье /1мф/ Изделие № 0475 (04, ш1600*в1035 мм)</t>
+          <t>Подиум Швеция, ДУБ /FP/ (1490*840*140 мм)</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>15700</v>
+        <v>17200</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>45882</v>
+        <v>45959</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2646,128 +2638,128 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>РОСКОСМОС</t>
+          <t>COMO (КОМО)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1-33156</t>
+          <t>1-33295</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>пн0453_4</t>
+          <t>0084</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Пуф прямоугольный /ЧП/ Изделие № 0453 (04, 800*400*450 мм)</t>
+          <t>Модуль FLAT Classic 2000*1000*400 опоры Массив</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>8750</v>
+        <v>109262</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>45889</v>
+        <v>45960</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Букин Владислав</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>РОСКОСМОС</t>
+          <t>проект 669 (ОРДЫНКА)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>3-33156</t>
+          <t>1-33296</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>пн0453_4</t>
+          <t>пн0505</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Кресло Винг с высокой спинкой /ЧП/ Изделие № 0453 (05, 665*750*1280 мм)</t>
+          <t>Кресло с низкой спинкой /ЧП/ Изделие №0505 (01)</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>55000</v>
+        <v>80000</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>45903</v>
+        <v>45999</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Харченко Дмитрий</t>
+          <t>Букин Владислав</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>РОСКОСМОС</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4-33156</t>
+          <t>1-33299</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>пн0453_4</t>
+          <t>зал</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Диван с высокой спинкой /ЧП/ Изделие № 0453 (06, 1440*800*1370 мм)</t>
+          <t>Евро-диван / "Марсель" / База / (сп.м. 1,9х1,5 м, ш.подл. 100 мм)</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>55000</v>
+        <v>36038</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>45895</v>
+        <v>45965</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Харьков Илья</t>
+          <t>Гуков Олег</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>РОСКОСМОС</t>
+          <t>Корт Инн</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5-33156</t>
+          <t>1-33309</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>пн0453_4</t>
+          <t>пн0127</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Кресло с полукруглой спинкой /ЧП/ Изделие № 0453 (07)</t>
+          <t>Кресло лаунж FF.05 /СЗМК/ Изделие № 0127 (01, 780*785*1185 мм)</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>23000</v>
+        <v>45000</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>45895</v>
+        <v>45984</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2778,62 +2770,62 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>COMO (КОМО)</t>
+          <t>Корт Инн</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7-25078</t>
+          <t>2-33309</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>062</t>
+          <t>пн0127</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Кровать Siena Kids с креплением к стене 1120*2130*670 (900*2000)</t>
+          <t>Кресло для рабочего стола с колесами FF.06 /СЗМК/ Изделие № 0127 (02, 650*650*750 мм)</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>93340</v>
+        <v>46800</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>45888</v>
+        <v>45987</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Харьков Илья</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Коломяжский</t>
+          <t>Корт Инн</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1-33157</t>
+          <t>3-33309</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>пн0051_1</t>
+          <t>пн0127</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Услуги по перетяжке и обивке (58, изголовье (МЯГКАЯ ЧАСТЬ) 2600*80*1100 мм, Коломяжский)</t>
+          <t>Бокс /СЗМК/ Изделие №0127 (03, 1800*2000*h290(300) мм)</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3800</v>
+        <v>20900</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>45896</v>
+        <v>45985</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2844,29 +2836,29 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Коломяжский</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2-33157</t>
+          <t>1-33314</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>пн0051_1</t>
+          <t>пн0000</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Услуги по перетяжке и обивке спринг бокса (59, 900*2000*h350 мм, высота борта - 250 мм, ножка - 100 мм Коломяжский)</t>
+          <t>Подушка декоративная / Стандарт / С молнией / (350х400 мм)</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2150</v>
+        <v>0</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>45896</v>
+        <v>45971</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2877,29 +2869,29 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Рыжий</t>
+          <t>Грибоедова (ДОРОС)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1-33161</t>
+          <t>1-33316</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>пн603_13</t>
+          <t>пн0062Пилот3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Услуги по реставрации левой части изголовья (63, вариант 1 (1150*2420 мм))</t>
+          <t>Кресло без поворотного механизма Грибоедова Дорос NOV + 100 мм (04)</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3500</v>
+        <v>32600</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>45918</v>
+        <v>45971</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2910,29 +2902,29 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>COMO (КОМО)</t>
+          <t>Грибоедова (ДОРОС)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1-33165</t>
+          <t>2-33316</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>0119</t>
+          <t>пн0062Пилот3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Кровать Siena kids стандартное Г образное  изголовье (СБОКУ) 1200*2000; 2120*1520*670h</t>
+          <t>Пуф овальный Грибоедова Дорос (05, 750*430*h430 мм)</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>110000</v>
+        <v>11800</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>45918</v>
+        <v>45971</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2943,29 +2935,29 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>COMO (КОМО)</t>
+          <t>Грибоедова (ДОРОС)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2-33165</t>
+          <t>3-33316</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0119</t>
+          <t>пн0062Пилот3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Банкетка к детской кровати Siena Kids (COMO) 1800*800*670</t>
+          <t>Пуф круглый Грибоедова Дорос (06, 430*h430 мм)</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>31700</v>
+        <v>8200</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>45918</v>
+        <v>45971</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2976,95 +2968,95 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ВИП Старостенко</t>
+          <t>Грибоедова (ДОРОС)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3-33167</t>
+          <t>4-33316</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>пн0476</t>
+          <t>пн0062Пилот3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Кровать детская с одним подлокотником /1мф/ Изделие № 0476 (03, 2056*998*h700 мм)</t>
+          <t>Реставрация стула реплика Calligaris FOYER (04)</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>45916</v>
+        <v>45978</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Букин Владислав</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ВИП Старостенко</t>
+          <t>Грибоедова (ДОРОС)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6-33167</t>
+          <t>5-33316</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>пн0476</t>
+          <t>пн0062Пилот3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Кровать детская с подлокотниками /1мф/ Изделие № 0476 (04, 2032*998*h700 мм)</t>
+          <t>Реставрация мягких элементов изголовья (05, комплект 4 верхние + 4 нижние вставки)</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>69000</v>
+        <v>14500</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>45917</v>
+        <v>45978</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Букин Владислав</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Грибоедова (ДОРОС)</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2-33168</t>
+          <t>1-33320</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>пн0062</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Спринг бокс 1500*2000*h350 мм (высота борта 270 мм, ножка 80 мм)</t>
+          <t>Подушка декоративная / Стандарт / Без молнии / (400х600 мм)</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>18100</v>
+        <v>1500</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>45901</v>
+        <v>45974</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3075,29 +3067,29 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Разовый заказ</t>
+          <t>Производственный холдинг</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1-24919</t>
+          <t>1-33319</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>пн0003</t>
+          <t>пн0516</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Чехол подушки декоративной / Стандарт / С молнией / Изделие №0003 (01,550*400 мм</t>
+          <t>Пуф /ЧП/ Изделие № 0516 (01,1600*500*450 мм)</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1800</v>
+        <v>20750</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>45891</v>
+        <v>45978</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3108,29 +3100,29 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Разовый заказ</t>
+          <t>МК Уровень</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3-24919</t>
+          <t>1-33324</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>пн0003</t>
+          <t>пн0519</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Чехол подушки декоративной / Стандарт / С молнией / Изделие №0003 (02,650*600 мм)</t>
+          <t>Стул /ЧП/ Изделие № 0519 (01, крашенная и некрашеная часть)</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2300</v>
+        <v>1500</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>45891</v>
+        <v>45978</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3141,29 +3133,29 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Разовый заказ</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>4-24919</t>
+          <t>1-33328</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>пн0003</t>
+          <t>с-1927</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Услуга по перетяжке и обивке стула (60)</t>
+          <t>Угловой диван / "Монреаль" / База /</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3500</v>
+        <v>29710</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>45891</v>
+        <v>45978</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3174,157 +3166,161 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Разовый заказ</t>
+          <t>ТЕО</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1-25117</t>
+          <t>1-33335</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>пн113</t>
+          <t>ПН 0521</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Услуги по перетяжке и обивке (61, стул Двинцев)</t>
+          <t>Софа 1200х1000</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>45891</v>
+        <v>45985</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Харченко Дмитрий</t>
+          <t>Букин Владислав</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Серийная мебель</t>
+          <t>ТЕО</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1-33175</t>
+          <t>2-33335</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>240  - 351</t>
+          <t>ПН 0521</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Кресло для отдыха / "Мадрид" / (ш.подл. 100 мм. на деревянных опорах орех 170 мм)</t>
+          <t>Пуф 1000x1000</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>19090</v>
+        <v>0</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>45895</v>
+        <v>45985</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Харьков Илья</t>
+          <t>Букин Владислав</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Консульская деревня</t>
+          <t>В.Шинкаренко</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>6-24848</t>
+          <t>1-33344</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>пн445</t>
+          <t>пн0140</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Услуги по перетяжке и обивке ( кресло Консульская деревня)</t>
+          <t>Спинка /СЗМК/ Изделие № 0140 (01,1150*350 мм)</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>14000</v>
+        <v>3900</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>45896</v>
+        <v>45988</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Харченко Дмитрий</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Консульская деревня</t>
+          <t>В.Шинкаренко</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7-24848</t>
+          <t>2-33344</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>пн445</t>
+          <t>пн0140</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Услуги по перетяжке и обивке ( пуфа Консульская деревня)</t>
+          <t>Сидушка /СЗМК/ Изделие № 0140 (02,1650*423 мм)</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>45896</v>
+        <v>45988</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Харченко Дмитрий</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Авенир Ладожский Дорос</t>
+          <t>Грибоедова (ДОРОС)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1-33179</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>4-33341</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>пн062_3</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Услуга по перетяжке и обивке бокса 900*2000 мм Авенир Ладожский</t>
+          <t>Мягкие элементы изголовья Грибоедова /СЗМК/ Изделие № 0062 (07, комплект 3 верхние + 3 нижние вставки)</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2550</v>
+        <v>28200</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>45896</v>
+        <v>45987</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3335,29 +3331,29 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Рыжий</t>
+          <t>Грибоедова (ДОРОС)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>4-24997</t>
+          <t>5-33341</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>пн603_12</t>
+          <t>пн062_3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Ножка буковая для бокса (150 мм, без колеса)</t>
+          <t>Мягкие элементы изголовья Грибоедова /СЗМК/ Изделие № 0062 (08, комплект 4 верхние + 4 нижние вставки)</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>340</v>
+        <v>37600</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>45903</v>
+        <v>45987</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3368,29 +3364,29 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VIDI</t>
+          <t>Грибоедова (ДОРОС)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2-33184</t>
+          <t>6-33341</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>пн284_3</t>
+          <t>пн062_3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Ножка буковая для бокса (150 мм, с колесом)</t>
+          <t>Мягкие элементы изголовья Грибоедова /СЗМК/ Изделие № 0062 (09, комплект 2 верхние + 2 нижние вставки)</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>450</v>
+        <v>18800</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>45903</v>
+        <v>45987</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3401,62 +3397,62 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Евгения от Петракова</t>
+          <t>FLUFFY&amp;PUFFY</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1-33192</t>
+          <t>1-33347</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>пн0484</t>
+          <t>пн945_4</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Кресло /ЧП/ Изделие № 0484 (01)</t>
+          <t>Стеновая панель 765*765 мм /FP/ Изделие №945 (02)</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>88000</v>
+        <v>2000</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>45906</v>
+        <v>45999</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Харченко Дмитрий</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Евгения от Петракова</t>
+          <t>FLUFFY&amp;PUFFY</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2-33192</t>
+          <t>2-33347</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>пн0484</t>
+          <t>пн945_4</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Кресло (зеркальное) /ЧП/ Изделие № 0484 (02)</t>
+          <t>Стеновая панель 760*190 мм /FP/ Изделие №945 (03)</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>55000</v>
+        <v>500</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>45904</v>
+        <v>45999</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3467,153 +3463,161 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Разовый заказ</t>
+          <t>FLUFFY&amp;PUFFY</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1-33193</t>
+          <t>3-33347</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>пн485</t>
+          <t>пн945_4</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Услуги по перетяжке и обивке (62, кровать ОБП)</t>
+          <t>Стеновая панель 765*380 мм /FP/ Изделие №945 (04)</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>12000</v>
+        <v>1000</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>45908</v>
+        <v>45999</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Харченко Дмитрий</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Серийная мебель</t>
+          <t>ЛУЧИ Анапа (Luchi Anapa)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1-33200</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
+          <t>1-33349</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>пн0128Пилот</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Услуги по перетяжке и обивке оттоманки дивана Монреаль 25069</t>
+          <t>Диван прямой /СЗМК/ Изделие №0128 (01, 2090х920мм)</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>48500</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>45908</v>
+        <v>46002</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Харченко Дмитрий</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Серийная мебель</t>
+          <t>ЛУЧИ Анапа (Luchi Anapa)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1-33202</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>3-33349</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>пн0128Пилот</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Перетяжка оттоманки дивана Монреаль 24942</t>
+          <t>Подушка-валик с молнией /СЗМК/ Изделие № 0128 (02, 650*d120-150 мм)</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="F96" s="1" t="n">
-        <v>45908</v>
+        <v>46002</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Харченко Дмитрий</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Сокольники</t>
+          <t>ЛУЧИ Анапа (Luchi Anapa)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1-33203</t>
+          <t>4-33349</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>пн0489</t>
+          <t>пн0128Пилот</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Зеркало d1500 мм</t>
+          <t>Бокс (03, 900*2000*h350-370 мм, высота царги не более 270 мм)</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>29500</v>
+        <v>14300</v>
       </c>
       <c r="F97" s="1" t="n">
-        <v>45908</v>
+        <v>46002</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Харченко Дмитрий</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Сергей Митхед</t>
+          <t>ЛУЧИ Анапа (Luchi Anapa)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1-33204</t>
+          <t>5-33349</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>пн0493</t>
+          <t>пн0128Пилот</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Комплект (спинки и сидушка) /ЧП/ Изделие № 0493 (01)</t>
+          <t>Подушка декоративная / Стандарт / С молнией / (700х400 мм)</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6000</v>
+        <v>1650</v>
       </c>
       <c r="F98" s="1" t="n">
-        <v>45918</v>
+        <v>46002</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3624,29 +3628,29 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>YES на Марата</t>
+          <t>ЛУЧИ Анапа (Luchi Anapa)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3-33205</t>
+          <t>6-33349</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>пн0014</t>
+          <t>пн0128Пилот</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Подушка подбагажника 689*538*65 мм</t>
+          <t>Подушка-валик с молнией /СЗМК/ Изделие № 0128 (04, 700*d120-150 мм)</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4100</v>
+        <v>2850</v>
       </c>
       <c r="F99" s="1" t="n">
-        <v>45919</v>
+        <v>46002</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3657,29 +3661,29 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Разовый заказ</t>
+          <t>ЛУЧИ Анапа (Luchi Anapa)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1-33207</t>
+          <t>7-33349</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>пн0490</t>
+          <t>пн0128Пилот</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Подбагажница /ЧП/ Изделие № 0490 (677*380*100 мм)</t>
+          <t>Саше на кровать /СЗМК/ Изделие №0128 (05)</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3900</v>
+        <v>3690</v>
       </c>
       <c r="F100" s="1" t="n">
-        <v>45916</v>
+        <v>46006</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3690,29 +3694,29 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>COMO (КОМО)</t>
+          <t>ЛУЧИ Анапа (Luchi Anapa)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1-33215</t>
+          <t>8-33349</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>0137</t>
+          <t>пн0128Пилот</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Пуф Bonbon 800*900*350 L</t>
+          <t>Тумба прикроватная /СЗМК/ Изделие №0128 (06)</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>14600</v>
+        <v>29000</v>
       </c>
       <c r="F101" s="1" t="n">
-        <v>45918</v>
+        <v>46006</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3723,62 +3727,62 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Пригожин (личное)</t>
+          <t>ЛУЧИ Анапа (Luchi Anapa)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1-33222</t>
+          <t>9-33349</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>110р</t>
+          <t>пн0128Пилот</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Пуговицы (желтые)</t>
+          <t>Пуф со спинкой (кресло) БЕЗ вращения /СЗМК/ Изделие №0128 (07)</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>50</v>
+        <v>31300</v>
       </c>
       <c r="F102" s="1" t="n">
-        <v>45919</v>
+        <v>46007</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Харьков Илья</t>
+          <t>Харченко Дмитрий</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Пригожин (личное)</t>
+          <t>Завидово</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2-33222</t>
+          <t>1-33351</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>110р</t>
+          <t>пн0498</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Пуговицы (синие)</t>
+          <t>Изголовье (мягкие элементы) /1мф/ Изделие №0498 (01, 1800*30*950 мм)</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>60</v>
+        <v>19900</v>
       </c>
       <c r="F103" s="1" t="n">
-        <v>45919</v>
+        <v>46002</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3789,29 +3793,29 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>COMO (КОМО)</t>
+          <t>Завидово</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3-33223</t>
+          <t>2-33351</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>0133</t>
+          <t>пн0498</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Кровать Siena Kids Г образная, с механизмом (1200*2000),  1820*2530*670</t>
+          <t>Спринг бокс /1мф/ Изделие №0498 (02,900*2000*320 мм, высота основания 170 мм, опора 150 мм.)</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>83000</v>
+        <v>13800</v>
       </c>
       <c r="F104" s="1" t="n">
-        <v>45930</v>
+        <v>46001</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3822,29 +3826,29 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Евгения от Петракова</t>
+          <t>Завидово</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1-33226</t>
+          <t>3-33351</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>пн0497</t>
+          <t>пн0498</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Пуф круглый /ЧП/ Изделие № 0497 (01, 400*400*450 мм)</t>
+          <t>Изголовье (крепится к боксу) /1мф/ Изделие №0498 (03, 900*30*950 мм)</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5500</v>
+        <v>10000</v>
       </c>
       <c r="F105" s="1" t="n">
-        <v>45919</v>
+        <v>46002</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -3855,29 +3859,29 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Евгения от Петракова</t>
+          <t>Завидово</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2-33226</t>
+          <t>4-33351</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>пн0497</t>
+          <t>пн0498</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Чехол на подставку для сумок и хлястик /ЧП/ Изделие №0497 (02)</t>
+          <t>Спринг бокс с усиленной фиксацией /1мф/ Изделие №0498 (04,900*2000*320 мм, высота основания 170 мм, опора 150 мм.)</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1000</v>
+        <v>14600</v>
       </c>
       <c r="F106" s="1" t="n">
-        <v>45919</v>
+        <v>46001</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -3888,29 +3892,29 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Серийная мебель</t>
+          <t>Завидово</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1-33228</t>
+          <t>5-33351</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>пн0498</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Евро-диван / "Монреаль" / База / (сп.м. 1,9х1,5 м, мягкий)</t>
+          <t>Изголовье (мягкие элементы) /1мф/ Изделие №0498 (05, 1600*30*950 мм)</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>44000</v>
+        <v>17800</v>
       </c>
       <c r="F107" s="1" t="n">
-        <v>45919</v>
+        <v>46002</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3921,29 +3925,29 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Серийная мебель</t>
+          <t>Завидово</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1-33227</t>
+          <t>6-33351</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>240-367</t>
+          <t>пн0498</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Угловой диван / "Монреаль" / База / (сп.м. 1,9х1,5 м, ф. 7, )</t>
+          <t>Спринг бокс /1мф/ Изделие №0498 (06,800*2000*320 мм, высота основания 170 мм, опора 150 мм.)</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>13300</v>
       </c>
       <c r="F108" s="1" t="n">
-        <v>45919</v>
+        <v>46001</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -3954,29 +3958,29 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>COMO (КОМО)</t>
+          <t>Грибоедова (ДОРОС)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1-33232</t>
+          <t>7-33341</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>122/1</t>
+          <t>пн062_3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Кровать Siena kids(como) с тонким L образным изголовьем, с подъемным механизмом (1200*2000), 1620*330*670)</t>
+          <t>Мягкие элементы изголовья Грибоедова НЕСТАНДАРТ /СЗМК/ Изделие № 0062 (10, комплект 4 верхние + 4 нижние вставки)</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>83000</v>
+        <v>37600</v>
       </c>
       <c r="F109" s="1" t="n">
-        <v>45919</v>
+        <v>45995</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -3987,128 +3991,128 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>УЛЬТРАМАР</t>
+          <t>Грибоедова (ДОРОС)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>4-33234</t>
+          <t>6-33346</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>пн0476</t>
+          <t>пн062_4</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Стол полубарный LATOS 3 /ЧП/ Изделие № 0476 (04, 1800*600*920 мм)</t>
+          <t>Мягкие элементы изголовья Грибоедова НЕСТАНДАРТ /СЗМК/ Изделие № 0062 (11, комплект 2 верхние + 2 нижние вставки)</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>90376</v>
+        <v>18800</v>
       </c>
       <c r="F110" s="1" t="n">
-        <v>45922</v>
+        <v>45995</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Харченко Дмитрий</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>УЛЬТРАМАР</t>
+          <t>Архыз</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5-33234</t>
+          <t>1-33325</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>пн0476</t>
+          <t>пн 0477</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Стол обеденный LATOS 1 /ЧП/ Изделие № 0476 (05, 1400*800*750 мм)</t>
+          <t>Бокс /1мф/ Изделие № 0477 (01, 1000*2000*h350 мм, царга-200мм, опора-150 мм)</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>74800</v>
+        <v>15000</v>
       </c>
       <c r="F111" s="1" t="n">
-        <v>45922</v>
+        <v>45995</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Харченко Дмитрий</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>УЛЬТРАМАР</t>
+          <t>Архыз</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>6-33234</t>
+          <t>3-33325</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>пн0476</t>
+          <t>пн 0477</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Стол обеденный LATOS 2 /ЧП/ Изделие № 0476 (05, 2200*800*750 мм)</t>
+          <t>Бокс /1мф/ Изделие № 0477 (03, 1600*2000*h350 мм, царга-200мм, опора-150 мм)</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>98560</v>
+        <v>21900</v>
       </c>
       <c r="F112" s="1" t="n">
-        <v>45922</v>
+        <v>45995</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Харченко Дмитрий</t>
+          <t>Харьков Илья</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ИКС-Холдинг</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2-33236</t>
+          <t>1-33355</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>пн0494</t>
+          <t>1907/2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Пуф прямоугольный /ЧП/ Изделие № 0494 (02, 600*400*450 мм)</t>
+          <t>подушка к дивану Манчестер</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="F113" s="1" t="n">
-        <v>45924</v>
+        <v>45999</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -4119,29 +4123,29 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>COMO (КОМО)</t>
+          <t>ВАРШАВКА В4</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>4-33223</t>
+          <t>7-25000</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>0133</t>
+          <t>пн0917</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Кровать Siena Kids L образная,без механизма 1200*2000 (1200*2000 мм, 1820*2530*670)</t>
+          <t>3d панель в нишу /FP/ Изделие №0917 (07, 4000*2500 мм)</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>83000</v>
+        <v>155040</v>
       </c>
       <c r="F114" s="1" t="n">
-        <v>45924</v>
+        <v>45999</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4152,29 +4156,29 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ПЕРВЫЙ</t>
+          <t>Серийная мебель</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1-33209</t>
+          <t>2-33355</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>пн0487</t>
+          <t>1907/2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Подушка двухсторонняя с утяжками, БЕЗ пуговиц /ЧП/ Изделие № 0487 (01, 300*600 мм)</t>
+          <t>Подушка декоративная / FP / Изделие № 460 (02, 400*400)</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3789.66</v>
+        <v>0</v>
       </c>
       <c r="F115" s="1" t="n">
-        <v>45930</v>
+        <v>46000</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4185,29 +4189,29 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Разовый заказ</t>
+          <t>Для Ильи</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1-33244</t>
+          <t>1-33366</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>пн0498</t>
+          <t>пн0114р</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Спинка + сидушка (комплект) /ЧП/ Изделие № 0498 (01)</t>
+          <t>Реставрация НОГстула Mad Diwing (Мэд Дайвинг)</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="F116" s="1" t="n">
-        <v>45930</v>
+        <v>46000</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4218,29 +4222,29 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Разовый заказ</t>
+          <t>YES Технопарк</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1-33246</t>
+          <t>2-33357</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>пн0129</t>
+          <t>пн0083_2</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Реставрация кресла (01)</t>
+          <t>Спинка длинная с закладными под Ф-Г /СЗМК/ Изделие № 0083 (06)</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5800</v>
+        <v>0</v>
       </c>
       <c r="F117" s="1" t="n">
-        <v>45930</v>
+        <v>46013</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4251,29 +4255,29 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Разовый заказ</t>
+          <t>YES Технопарк</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2-33246</t>
+          <t>3-33357</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>пн0129</t>
+          <t>пн0083_2</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Реставрация барный стул (02)</t>
+          <t>Спинка короткая с закладными под Ф-Г/СЗМК/ Изделие № 0083 (07)</t>
         </is>
       </c>
       <c r="E118" t="n">
         <v>0</v>
       </c>
       <c r="F118" s="1" t="n">
-        <v>45930</v>
+        <v>46013</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -4284,29 +4288,29 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Разовый заказ</t>
+          <t>YES Технопарк</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3-33246</t>
+          <t>5-33357</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>пн0129</t>
+          <t>пн0083_2</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Реставрация пуф (03)</t>
+          <t>Спинка длинная с закладными под Ф-7 /СЗМК/ Изделие № 0083 (09)</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>8500</v>
+        <v>0</v>
       </c>
       <c r="F119" s="1" t="n">
-        <v>45930</v>
+        <v>46013</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -4317,31 +4321,192 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Разовый заказ</t>
+          <t>YES Технопарк</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>4-33246</t>
+          <t>6-33357</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>пн0129</t>
+          <t>пн0083_2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Реставрация кресло Дайтвердер (03)</t>
+          <t>Спинка короткая с закладными под Ф-7/СЗМК/ Изделие № 0083 (10)</t>
         </is>
       </c>
       <c r="E120" t="n">
         <v>0</v>
       </c>
       <c r="F120" s="1" t="n">
-        <v>45930</v>
+        <v>46013</v>
       </c>
       <c r="G120" t="inlineStr">
+        <is>
+          <t>Харьков Илья</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Сокольники</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2-33203</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>пн0489</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Услуги по изготовлению брезента</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F121" s="1" t="n">
+        <v>46012</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Харченко Дмитрий</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Сокольники</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>3-33203</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>пн0489</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Реставрация инсталяции</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F122" s="1" t="n">
+        <v>46012</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Харченко Дмитрий</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Громово</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1-33385</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>пн115р</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Рекламация изголовья кровати Siena (COMO) стандартное (одинарное) тонкое изголовье 2330*1820х670h (1600*2000 мм)</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="1" t="n">
+        <v>46012</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Харченко Дмитрий</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Громово</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>5-33385</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>пн115р</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Рекламация изголовья кровати Siena  (одинарное) тонкое изголовье 2330*1820х820h (1600*2000 мм, 2020*2330*820) с подъемным механизмом</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="1" t="n">
+        <v>46012</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Харченко Дмитрий</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Саша Югай</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1-33360</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Ступень ДУБ</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>9272.73</v>
+      </c>
+      <c r="F125" s="1" t="n">
+        <v>46014</v>
+      </c>
+      <c r="G125" t="inlineStr">
         <is>
           <t>Харьков Илья</t>
         </is>
